--- a/ячейка96(10 дней).xlsx
+++ b/ячейка96(10 дней).xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Eduard\#Work\2019_Sygyktinsky\Model\DSEBM\Зорин\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skibc\PycharmProjects\ZORIN grass 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F2FEE2C-8187-4C3A-801C-A9AFF38EBCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED56A54D-B4DA-4A41-82E1-8408ACEF157F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{41652E5A-C04B-41B8-B8AF-E4D3B08BB20D}"/>
+    <workbookView xWindow="3825" yWindow="3285" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{41652E5A-C04B-41B8-B8AF-E4D3B08BB20D}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -383,10 +387,1208 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист2!$A$1:$A$48</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="48"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13.8429</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.434699999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>35.100700000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45.506999999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>32.2926</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>80.984499999999997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>139.16999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>204.679</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>275.43900000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>349.464</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>424.86599999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>499.86200000000002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>572.779</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>642.06600000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>706.298</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>764.17499999999995</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>814.53200000000004</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>856.33399999999995</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>888.68799999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>910.83799999999997</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>922.18</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>922.26400000000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>910.80700000000002</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>887.70500000000004</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>853.048</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>807.13699999999994</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>750.49800000000005</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>683.90099999999995</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>608.38099999999997</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>64.416799999999995</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>55.3596</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>45.506999999999998</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>35.100700000000003</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>24.434699999999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>13.8429</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A884-42DE-92AF-85D2EF60A234}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист2!$B$1:$B$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="48"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13.84</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.43</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>35.1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45.51</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>32.29</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>80.98</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>139.16999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>204.68</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>275.44</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>349.46</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>424.87</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>499.86</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>572.78</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>642.07000000000005</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>706.3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>764.18</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>814.53</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>856.33</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>888.69</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>910.84</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>922.18</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>922.26</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>910.81</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>887.7</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>853.05</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>807.14</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>750.5</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>683.9</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>608.38</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>64.42</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>55.36</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>45.51</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>35.1</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>24.43</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>13.84</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A884-42DE-92AF-85D2EF60A234}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1442343360"/>
+        <c:axId val="1442347680"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1442343360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1442347680"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1442347680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1442343360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F2261A5-5D45-7F76-FAFD-22CB8557E4A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -424,7 +1626,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -530,7 +1732,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -672,7 +1874,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -681,19 +1883,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D808A9-4FC2-4C50-A03A-A0AF2327DBB2}">
   <dimension ref="A1:S483"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="17.109375" customWidth="1"/>
-    <col min="16" max="16" width="13.77734375" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" customWidth="1"/>
-    <col min="18" max="18" width="15.33203125" customWidth="1"/>
-    <col min="19" max="19" width="16.21875" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" customWidth="1"/>
+    <col min="15" max="15" width="17.140625" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" customWidth="1"/>
+    <col min="19" max="19" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="144" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
@@ -744,7 +1946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="17.25" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
       <c r="F2" s="8" t="s">
         <v>15</v>
@@ -786,7 +1988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="44.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -845,7 +2047,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>43653</v>
       </c>
@@ -904,7 +2106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>43653</v>
       </c>
@@ -963,7 +2165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>43653</v>
       </c>
@@ -1022,7 +2224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>43653</v>
       </c>
@@ -1081,7 +2283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>43653</v>
       </c>
@@ -1140,7 +2342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>43653</v>
       </c>
@@ -1199,7 +2401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>43653</v>
       </c>
@@ -1258,7 +2460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>43653</v>
       </c>
@@ -1317,7 +2519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>43653</v>
       </c>
@@ -1376,7 +2578,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>43653</v>
       </c>
@@ -1435,7 +2637,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>43653</v>
       </c>
@@ -1494,7 +2696,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>43653</v>
       </c>
@@ -1553,7 +2755,7 @@
         <v>145.1</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>43653</v>
       </c>
@@ -1612,7 +2814,7 @@
         <v>230.3</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>43653</v>
       </c>
@@ -1671,7 +2873,7 @@
         <v>295.59999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>43653</v>
       </c>
@@ -1730,7 +2932,7 @@
         <v>382.7</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>43653</v>
       </c>
@@ -1789,7 +2991,7 @@
         <v>455.2</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>43653</v>
       </c>
@@ -1848,7 +3050,7 @@
         <v>516.9</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>43653</v>
       </c>
@@ -1907,7 +3109,7 @@
         <v>589.4</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>43653</v>
       </c>
@@ -1966,7 +3168,7 @@
         <v>658.4</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>43653</v>
       </c>
@@ -2025,7 +3227,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>43653</v>
       </c>
@@ -2084,7 +3286,7 @@
         <v>783.5</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>43653</v>
       </c>
@@ -2143,7 +3345,7 @@
         <v>912.29999999999984</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>43653</v>
       </c>
@@ -2202,7 +3404,7 @@
         <v>890.5</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>43653</v>
       </c>
@@ -2261,7 +3463,7 @@
         <v>981.2</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>43653</v>
       </c>
@@ -2320,7 +3522,7 @@
         <v>955.8</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>43653</v>
       </c>
@@ -2379,7 +3581,7 @@
         <v>1026.5</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>43653</v>
       </c>
@@ -2438,7 +3640,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>43653</v>
       </c>
@@ -2497,7 +3699,7 @@
         <v>714.6</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
         <v>43653</v>
       </c>
@@ -2556,7 +3758,7 @@
         <v>281.10000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
         <v>43653</v>
       </c>
@@ -2615,7 +3817,7 @@
         <v>272.10000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
         <v>43653</v>
       </c>
@@ -2674,7 +3876,7 @@
         <v>224.90000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
         <v>43653</v>
       </c>
@@ -2733,7 +3935,7 @@
         <v>252.10000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
         <v>43653</v>
       </c>
@@ -2792,7 +3994,7 @@
         <v>382.7</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
         <v>43653</v>
       </c>
@@ -2851,7 +4053,7 @@
         <v>275.7</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
         <v>43653</v>
       </c>
@@ -2910,7 +4112,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>43653</v>
       </c>
@@ -2969,7 +4171,7 @@
         <v>110.6</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <v>43653</v>
       </c>
@@ -3028,7 +4230,7 @@
         <v>101.6</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <v>43653</v>
       </c>
@@ -3087,7 +4289,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
         <v>43653</v>
       </c>
@@ -3146,7 +4348,7 @@
         <v>49.000000000000007</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <v>43653</v>
       </c>
@@ -3205,7 +4407,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <v>43653</v>
       </c>
@@ -3264,7 +4466,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <v>43653</v>
       </c>
@@ -3323,7 +4525,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <v>43653</v>
       </c>
@@ -3382,7 +4584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
         <v>43653</v>
       </c>
@@ -3441,7 +4643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
         <v>43653</v>
       </c>
@@ -3500,7 +4702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <v>43653</v>
       </c>
@@ -3559,7 +4761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
         <v>43653</v>
       </c>
@@ -3618,7 +4820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <v>43653</v>
       </c>
@@ -3677,7 +4879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="21">
         <v>43654</v>
       </c>
@@ -3736,7 +4938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="21">
         <v>43654</v>
       </c>
@@ -3795,7 +4997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="21">
         <v>43654</v>
       </c>
@@ -3854,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="21">
         <v>43654</v>
       </c>
@@ -3913,7 +5115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="21">
         <v>43654</v>
       </c>
@@ -3972,7 +5174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="21">
         <v>43654</v>
       </c>
@@ -4031,7 +5233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="21">
         <v>43654</v>
       </c>
@@ -4090,7 +5292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="21">
         <v>43654</v>
       </c>
@@ -4149,7 +5351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="21">
         <v>43654</v>
       </c>
@@ -4208,7 +5410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="21">
         <v>43654</v>
       </c>
@@ -4267,7 +5469,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="21">
         <v>43654</v>
       </c>
@@ -4326,7 +5528,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="21">
         <v>43654</v>
       </c>
@@ -4385,7 +5587,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="21">
         <v>43654</v>
       </c>
@@ -4444,7 +5646,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="21">
         <v>43654</v>
       </c>
@@ -4503,7 +5705,7 @@
         <v>110.6</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="21">
         <v>43654</v>
       </c>
@@ -4562,7 +5764,7 @@
         <v>186.8</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="21">
         <v>43654</v>
       </c>
@@ -4621,7 +5823,7 @@
         <v>183.2</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="21">
         <v>43654</v>
       </c>
@@ -4680,7 +5882,7 @@
         <v>110.6</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="21">
         <v>43654</v>
       </c>
@@ -4739,7 +5941,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="21">
         <v>43654</v>
       </c>
@@ -4798,7 +6000,7 @@
         <v>235.8</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="21">
         <v>43654</v>
       </c>
@@ -4857,7 +6059,7 @@
         <v>170.5</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="21">
         <v>43654</v>
       </c>
@@ -4916,7 +6118,7 @@
         <v>175.9</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="21">
         <v>43654</v>
       </c>
@@ -4975,7 +6177,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="21">
         <v>43654</v>
       </c>
@@ -5034,7 +6236,7 @@
         <v>558.6</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="21">
         <v>43654</v>
       </c>
@@ -5093,7 +6295,7 @@
         <v>480.6</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="21">
         <v>43654</v>
       </c>
@@ -5152,7 +6354,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="21">
         <v>43654</v>
       </c>
@@ -5211,7 +6413,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="21">
         <v>43654</v>
       </c>
@@ -5270,7 +6472,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="21">
         <v>43654</v>
       </c>
@@ -5329,7 +6531,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="21">
         <v>43654</v>
       </c>
@@ -5388,7 +6590,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="21">
         <v>43654</v>
       </c>
@@ -5447,7 +6649,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="21">
         <v>43654</v>
       </c>
@@ -5506,7 +6708,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="21">
         <v>43654</v>
       </c>
@@ -5565,7 +6767,7 @@
         <v>235.8</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="21">
         <v>43654</v>
       </c>
@@ -5624,7 +6826,7 @@
         <v>248.5</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="21">
         <v>43654</v>
       </c>
@@ -5683,7 +6885,7 @@
         <v>152.30000000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="21">
         <v>43654</v>
       </c>
@@ -5742,7 +6944,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="21">
         <v>43654</v>
       </c>
@@ -5801,7 +7003,7 @@
         <v>141.5</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="21">
         <v>43654</v>
       </c>
@@ -5860,7 +7062,7 @@
         <v>88.9</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="21">
         <v>43654</v>
       </c>
@@ -5919,7 +7121,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="21">
         <v>43654</v>
       </c>
@@ -5978,7 +7180,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="21">
         <v>43654</v>
       </c>
@@ -6037,7 +7239,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="21">
         <v>43654</v>
       </c>
@@ -6096,7 +7298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="21">
         <v>43654</v>
       </c>
@@ -6155,7 +7357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="21">
         <v>43654</v>
       </c>
@@ -6214,7 +7416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="21">
         <v>43654</v>
       </c>
@@ -6273,7 +7475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="21">
         <v>43654</v>
       </c>
@@ -6332,7 +7534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="21">
         <v>43654</v>
       </c>
@@ -6391,7 +7593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="21">
         <v>43654</v>
       </c>
@@ -6450,7 +7652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="21">
         <v>43654</v>
       </c>
@@ -6509,7 +7711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="21">
         <v>43655</v>
       </c>
@@ -6568,7 +7770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="21">
         <v>43655</v>
       </c>
@@ -6627,7 +7829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="21">
         <v>43655</v>
       </c>
@@ -6686,7 +7888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="21">
         <v>43655</v>
       </c>
@@ -6745,7 +7947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" s="21">
         <v>43655</v>
       </c>
@@ -6804,7 +8006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="21">
         <v>43655</v>
       </c>
@@ -6863,7 +8065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="21">
         <v>43655</v>
       </c>
@@ -6922,7 +8124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="21">
         <v>43655</v>
       </c>
@@ -6981,7 +8183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="21">
         <v>43655</v>
       </c>
@@ -7040,7 +8242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="21">
         <v>43655</v>
       </c>
@@ -7099,7 +8301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="21">
         <v>43655</v>
       </c>
@@ -7158,7 +8360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="21">
         <v>43655</v>
       </c>
@@ -7217,7 +8419,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="21">
         <v>43655</v>
       </c>
@@ -7276,7 +8478,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="21">
         <v>43655</v>
       </c>
@@ -7335,7 +8537,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="21">
         <v>43655</v>
       </c>
@@ -7394,7 +8596,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="21">
         <v>43655</v>
       </c>
@@ -7453,7 +8655,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="21">
         <v>43655</v>
       </c>
@@ -7512,7 +8714,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="21">
         <v>43655</v>
       </c>
@@ -7571,7 +8773,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="21">
         <v>43655</v>
       </c>
@@ -7630,7 +8832,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="21">
         <v>43655</v>
       </c>
@@ -7689,7 +8891,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="21">
         <v>43655</v>
       </c>
@@ -7748,7 +8950,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="21">
         <v>43655</v>
       </c>
@@ -7807,7 +9009,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="21">
         <v>43655</v>
       </c>
@@ -7866,7 +9068,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="21">
         <v>43655</v>
       </c>
@@ -7925,7 +9127,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="21">
         <v>43655</v>
       </c>
@@ -7984,7 +9186,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" s="21">
         <v>43655</v>
       </c>
@@ -8043,7 +9245,7 @@
         <v>119.7</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="21">
         <v>43655</v>
       </c>
@@ -8102,7 +9304,7 @@
         <v>88.9</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="21">
         <v>43655</v>
       </c>
@@ -8161,7 +9363,7 @@
         <v>132.4</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="21">
         <v>43655</v>
       </c>
@@ -8220,7 +9422,7 @@
         <v>154.19999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" s="21">
         <v>43655</v>
       </c>
@@ -8279,7 +9481,7 @@
         <v>382.7</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" s="21">
         <v>43655</v>
       </c>
@@ -8338,7 +9540,7 @@
         <v>94.3</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" s="21">
         <v>43655</v>
       </c>
@@ -8397,7 +9599,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" s="21">
         <v>43655</v>
       </c>
@@ -8456,7 +9658,7 @@
         <v>79.8</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" s="21">
         <v>43655</v>
       </c>
@@ -8515,7 +9717,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" s="21">
         <v>43655</v>
       </c>
@@ -8574,7 +9776,7 @@
         <v>88.9</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" s="21">
         <v>43655</v>
       </c>
@@ -8633,7 +9835,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" s="21">
         <v>43655</v>
       </c>
@@ -8692,7 +9894,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" s="21">
         <v>43655</v>
       </c>
@@ -8751,7 +9953,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" s="21">
         <v>43655</v>
       </c>
@@ -8810,7 +10012,7 @@
         <v>14.500000000000002</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" s="21">
         <v>43655</v>
       </c>
@@ -8869,7 +10071,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" s="21">
         <v>43655</v>
       </c>
@@ -8928,7 +10130,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" s="21">
         <v>43655</v>
       </c>
@@ -8987,7 +10189,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" s="21">
         <v>43655</v>
       </c>
@@ -9046,7 +10248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" s="21">
         <v>43655</v>
       </c>
@@ -9105,7 +10307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" s="21">
         <v>43655</v>
       </c>
@@ -9164,7 +10366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" s="21">
         <v>43655</v>
       </c>
@@ -9223,7 +10425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" s="21">
         <v>43655</v>
       </c>
@@ -9282,7 +10484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" s="21">
         <v>43655</v>
       </c>
@@ -9341,7 +10543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" s="21">
         <v>43656</v>
       </c>
@@ -9400,7 +10602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" s="21">
         <v>43656</v>
       </c>
@@ -9459,7 +10661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" s="21">
         <v>43656</v>
       </c>
@@ -9518,7 +10720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" s="21">
         <v>43656</v>
       </c>
@@ -9577,7 +10779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" s="21">
         <v>43656</v>
       </c>
@@ -9636,7 +10838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" s="21">
         <v>43656</v>
       </c>
@@ -9695,7 +10897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" s="21">
         <v>43656</v>
       </c>
@@ -9754,7 +10956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" s="21">
         <v>43656</v>
       </c>
@@ -9813,7 +11015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" s="21">
         <v>43656</v>
       </c>
@@ -9872,7 +11074,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" s="21">
         <v>43656</v>
       </c>
@@ -9931,7 +11133,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" s="21">
         <v>43656</v>
       </c>
@@ -9990,7 +11192,7 @@
         <v>116.10000000000001</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" s="21">
         <v>43656</v>
       </c>
@@ -10049,7 +11251,7 @@
         <v>175.9</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" s="21">
         <v>43656</v>
       </c>
@@ -10108,7 +11310,7 @@
         <v>248.5</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" s="21">
         <v>43656</v>
       </c>
@@ -10167,7 +11369,7 @@
         <v>295.60000000000002</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" s="21">
         <v>43656</v>
       </c>
@@ -10226,7 +11428,7 @@
         <v>366.4</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" s="21">
         <v>43656</v>
       </c>
@@ -10285,7 +11487,7 @@
         <v>444.4</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" s="21">
         <v>43656</v>
       </c>
@@ -10344,7 +11546,7 @@
         <v>527.79999999999995</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" s="21">
         <v>43656</v>
       </c>
@@ -10403,7 +11605,7 @@
         <v>594.9</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" s="21">
         <v>43656</v>
       </c>
@@ -10462,7 +11664,7 @@
         <v>663.8</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" s="21">
         <v>43656</v>
       </c>
@@ -10521,7 +11723,7 @@
         <v>721.8</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" s="21">
         <v>43656</v>
       </c>
@@ -10580,7 +11782,7 @@
         <v>787.1</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" s="21">
         <v>43656</v>
       </c>
@@ -10639,7 +11841,7 @@
         <v>839.7</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" s="21">
         <v>43656</v>
       </c>
@@ -10698,7 +11900,7 @@
         <v>877.79999999999984</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" s="21">
         <v>43656</v>
       </c>
@@ -10757,7 +11959,7 @@
         <v>228.5</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" s="21">
         <v>43656</v>
       </c>
@@ -10816,7 +12018,7 @@
         <v>253.90000000000003</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" s="21">
         <v>43656</v>
       </c>
@@ -10875,7 +12077,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" s="21">
         <v>43656</v>
       </c>
@@ -10934,7 +12136,7 @@
         <v>179.6</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" s="21">
         <v>43656</v>
       </c>
@@ -10993,7 +12195,7 @@
         <v>121.49999999999999</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" s="21">
         <v>43656</v>
       </c>
@@ -11052,7 +12254,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" s="21">
         <v>43656</v>
       </c>
@@ -11111,7 +12313,7 @@
         <v>181.4</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" s="21">
         <v>43656</v>
       </c>
@@ -11170,7 +12372,7 @@
         <v>152.30000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" s="21">
         <v>43656</v>
       </c>
@@ -11229,7 +12431,7 @@
         <v>348.2</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" s="21">
         <v>43656</v>
       </c>
@@ -11288,7 +12490,7 @@
         <v>234.00000000000003</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" s="21">
         <v>43656</v>
       </c>
@@ -11347,7 +12549,7 @@
         <v>219.5</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" s="21">
         <v>43656</v>
       </c>
@@ -11406,7 +12608,7 @@
         <v>161.4</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" s="21">
         <v>43656</v>
       </c>
@@ -11465,7 +12667,7 @@
         <v>275.7</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" s="21">
         <v>43656</v>
       </c>
@@ -11524,7 +12726,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" s="21">
         <v>43656</v>
       </c>
@@ -11583,7 +12785,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" s="21">
         <v>43656</v>
       </c>
@@ -11642,7 +12844,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" s="21">
         <v>43656</v>
       </c>
@@ -11701,7 +12903,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" s="21">
         <v>43656</v>
       </c>
@@ -11760,7 +12962,7 @@
         <v>12.699999999999998</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" s="21">
         <v>43656</v>
       </c>
@@ -11819,7 +13021,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" s="21">
         <v>43656</v>
       </c>
@@ -11878,7 +13080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" s="21">
         <v>43656</v>
       </c>
@@ -11937,7 +13139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" s="21">
         <v>43656</v>
       </c>
@@ -11996,7 +13198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" s="21">
         <v>43656</v>
       </c>
@@ -12055,7 +13257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" s="21">
         <v>43656</v>
       </c>
@@ -12114,7 +13316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" s="21">
         <v>43656</v>
       </c>
@@ -12173,7 +13375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" s="21">
         <v>43657</v>
       </c>
@@ -12232,7 +13434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" s="21">
         <v>43657</v>
       </c>
@@ -12291,7 +13493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" s="21">
         <v>43657</v>
       </c>
@@ -12350,7 +13552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" s="21">
         <v>43657</v>
       </c>
@@ -12409,7 +13611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" s="21">
         <v>43657</v>
       </c>
@@ -12468,7 +13670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" s="21">
         <v>43657</v>
       </c>
@@ -12527,7 +13729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" s="21">
         <v>43657</v>
       </c>
@@ -12586,7 +13788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" s="21">
         <v>43657</v>
       </c>
@@ -12645,7 +13847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" s="21">
         <v>43657</v>
       </c>
@@ -12704,7 +13906,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" s="21">
         <v>43657</v>
       </c>
@@ -12763,7 +13965,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" s="21">
         <v>43657</v>
       </c>
@@ -12822,7 +14024,7 @@
         <v>70.7</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" s="21">
         <v>43657</v>
       </c>
@@ -12881,7 +14083,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" s="21">
         <v>43657</v>
       </c>
@@ -12940,7 +14142,7 @@
         <v>117.9</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" s="21">
         <v>43657</v>
       </c>
@@ -12999,7 +14201,7 @@
         <v>248.5</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A210" s="21">
         <v>43657</v>
       </c>
@@ -13058,7 +14260,7 @@
         <v>195.9</v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A211" s="21">
         <v>43657</v>
       </c>
@@ -13117,7 +14319,7 @@
         <v>154.19999999999999</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" s="21">
         <v>43657</v>
       </c>
@@ -13176,7 +14378,7 @@
         <v>145.1</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A213" s="21">
         <v>43657</v>
       </c>
@@ -13235,7 +14437,7 @@
         <v>192.2</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A214" s="21">
         <v>43657</v>
       </c>
@@ -13294,7 +14496,7 @@
         <v>166.9</v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A215" s="21">
         <v>43657</v>
       </c>
@@ -13353,7 +14555,7 @@
         <v>208.6</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" s="21">
         <v>43657</v>
       </c>
@@ -13412,7 +14614,7 @@
         <v>228.5</v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" s="21">
         <v>43657</v>
       </c>
@@ -13471,7 +14673,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" s="21">
         <v>43657</v>
       </c>
@@ -13530,7 +14732,7 @@
         <v>279.3</v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" s="21">
         <v>43657</v>
       </c>
@@ -13589,7 +14791,7 @@
         <v>266.60000000000002</v>
       </c>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" s="21">
         <v>43657</v>
       </c>
@@ -13648,7 +14850,7 @@
         <v>192.2</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" s="21">
         <v>43657</v>
       </c>
@@ -13707,7 +14909,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" s="21">
         <v>43657</v>
       </c>
@@ -13766,7 +14968,7 @@
         <v>284.7</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" s="21">
         <v>43657</v>
       </c>
@@ -13825,7 +15027,7 @@
         <v>186.8</v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" s="21">
         <v>43657</v>
       </c>
@@ -13884,7 +15086,7 @@
         <v>177.7</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A225" s="21">
         <v>43657</v>
       </c>
@@ -13943,7 +15145,7 @@
         <v>192.2</v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A226" s="21">
         <v>43657</v>
       </c>
@@ -14002,7 +15204,7 @@
         <v>137.80000000000001</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A227" s="21">
         <v>43657</v>
       </c>
@@ -14061,7 +15263,7 @@
         <v>219.5</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A228" s="21">
         <v>43657</v>
       </c>
@@ -14120,7 +15322,7 @@
         <v>190.4</v>
       </c>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A229" s="21">
         <v>43657</v>
       </c>
@@ -14179,7 +15381,7 @@
         <v>248.5</v>
       </c>
     </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A230" s="21">
         <v>43657</v>
       </c>
@@ -14238,7 +15440,7 @@
         <v>188.6</v>
       </c>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A231" s="21">
         <v>43657</v>
       </c>
@@ -14297,7 +15499,7 @@
         <v>210.4</v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A232" s="21">
         <v>43657</v>
       </c>
@@ -14356,7 +15558,7 @@
         <v>137.80000000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A233" s="21">
         <v>43657</v>
       </c>
@@ -14415,7 +15617,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A234" s="21">
         <v>43657</v>
       </c>
@@ -14474,7 +15676,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A235" s="21">
         <v>43657</v>
       </c>
@@ -14533,7 +15735,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A236" s="21">
         <v>43657</v>
       </c>
@@ -14592,7 +15794,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A237" s="21">
         <v>43657</v>
       </c>
@@ -14651,7 +15853,7 @@
         <v>1.8000000000000003</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A238" s="21">
         <v>43657</v>
       </c>
@@ -14710,7 +15912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A239" s="21">
         <v>43657</v>
       </c>
@@ -14769,7 +15971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A240" s="21">
         <v>43657</v>
       </c>
@@ -14828,7 +16030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A241" s="21">
         <v>43657</v>
       </c>
@@ -14887,7 +16089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A242" s="21">
         <v>43657</v>
       </c>
@@ -14946,7 +16148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A243" s="21">
         <v>43657</v>
       </c>
@@ -15005,7 +16207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A244" s="21">
         <v>43658</v>
       </c>
@@ -15064,7 +16266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A245" s="21">
         <v>43658</v>
       </c>
@@ -15123,7 +16325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A246" s="21">
         <v>43658</v>
       </c>
@@ -15182,7 +16384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A247" s="21">
         <v>43658</v>
       </c>
@@ -15241,7 +16443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A248" s="21">
         <v>43658</v>
       </c>
@@ -15300,7 +16502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A249" s="21">
         <v>43658</v>
       </c>
@@ -15359,7 +16561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A250" s="21">
         <v>43658</v>
       </c>
@@ -15418,7 +16620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A251" s="21">
         <v>43658</v>
       </c>
@@ -15477,7 +16679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A252" s="21">
         <v>43658</v>
       </c>
@@ -15536,7 +16738,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A253" s="21">
         <v>43658</v>
       </c>
@@ -15595,7 +16797,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A254" s="21">
         <v>43658</v>
       </c>
@@ -15654,7 +16856,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A255" s="21">
         <v>43658</v>
       </c>
@@ -15713,7 +16915,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A256" s="21">
         <v>43658</v>
       </c>
@@ -15772,7 +16974,7 @@
         <v>342.8</v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A257" s="21">
         <v>43658</v>
       </c>
@@ -15831,7 +17033,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A258" s="21">
         <v>43658</v>
       </c>
@@ -15890,7 +17092,7 @@
         <v>59.9</v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A259" s="21">
         <v>43658</v>
       </c>
@@ -15949,7 +17151,7 @@
         <v>466.1</v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A260" s="21">
         <v>43658</v>
       </c>
@@ -16008,7 +17210,7 @@
         <v>515.1</v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A261" s="21">
         <v>43658</v>
       </c>
@@ -16067,7 +17269,7 @@
         <v>288.39999999999998</v>
       </c>
     </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A262" s="21">
         <v>43658</v>
       </c>
@@ -16126,7 +17328,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A263" s="21">
         <v>43658</v>
       </c>
@@ -16185,7 +17387,7 @@
         <v>295.60000000000002</v>
       </c>
     </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A264" s="21">
         <v>43658</v>
       </c>
@@ -16244,7 +17446,7 @@
         <v>478.8</v>
       </c>
     </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A265" s="21">
         <v>43658</v>
       </c>
@@ -16303,7 +17505,7 @@
         <v>886.9</v>
       </c>
     </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A266" s="21">
         <v>43658</v>
       </c>
@@ -16362,7 +17564,7 @@
         <v>183.2</v>
       </c>
     </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A267" s="21">
         <v>43658</v>
       </c>
@@ -16421,7 +17623,7 @@
         <v>97.9</v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A268" s="21">
         <v>43658</v>
       </c>
@@ -16480,7 +17682,7 @@
         <v>99.8</v>
       </c>
     </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A269" s="21">
         <v>43658</v>
       </c>
@@ -16539,7 +17741,7 @@
         <v>301.10000000000002</v>
       </c>
     </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A270" s="21">
         <v>43658</v>
       </c>
@@ -16598,7 +17800,7 @@
         <v>1024.7</v>
       </c>
     </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A271" s="21">
         <v>43658</v>
       </c>
@@ -16657,7 +17859,7 @@
         <v>674.7</v>
       </c>
     </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A272" s="21">
         <v>43658</v>
       </c>
@@ -16716,7 +17918,7 @@
         <v>923.2</v>
       </c>
     </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A273" s="21">
         <v>43658</v>
       </c>
@@ -16775,7 +17977,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A274" s="21">
         <v>43658</v>
       </c>
@@ -16834,7 +18036,7 @@
         <v>76.2</v>
       </c>
     </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A275" s="21">
         <v>43658</v>
       </c>
@@ -16893,7 +18095,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A276" s="21">
         <v>43658</v>
       </c>
@@ -16952,7 +18154,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A277" s="21">
         <v>43658</v>
       </c>
@@ -17011,7 +18213,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A278" s="21">
         <v>43658</v>
       </c>
@@ -17070,7 +18272,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A279" s="21">
         <v>43658</v>
       </c>
@@ -17129,7 +18331,7 @@
         <v>108.8</v>
       </c>
     </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A280" s="21">
         <v>43658</v>
       </c>
@@ -17188,7 +18390,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A281" s="21">
         <v>43658</v>
       </c>
@@ -17247,7 +18449,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A282" s="21">
         <v>43658</v>
       </c>
@@ -17306,7 +18508,7 @@
         <v>36.299999999999997</v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A283" s="21">
         <v>43658</v>
       </c>
@@ -17365,7 +18567,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A284" s="21">
         <v>43658</v>
       </c>
@@ -17424,7 +18626,7 @@
         <v>14.499999999999998</v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A285" s="21">
         <v>43658</v>
       </c>
@@ -17483,7 +18685,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A286" s="21">
         <v>43658</v>
       </c>
@@ -17542,7 +18744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A287" s="21">
         <v>43658</v>
       </c>
@@ -17601,7 +18803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A288" s="21">
         <v>43658</v>
       </c>
@@ -17660,7 +18862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A289" s="21">
         <v>43658</v>
       </c>
@@ -17719,7 +18921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A290" s="21">
         <v>43658</v>
       </c>
@@ -17778,7 +18980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A291" s="21">
         <v>43658</v>
       </c>
@@ -17837,7 +19039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A292" s="21">
         <v>43659</v>
       </c>
@@ -17896,7 +19098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A293" s="21">
         <v>43659</v>
       </c>
@@ -17955,7 +19157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A294" s="21">
         <v>43659</v>
       </c>
@@ -18014,7 +19216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A295" s="21">
         <v>43659</v>
       </c>
@@ -18073,7 +19275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A296" s="21">
         <v>43659</v>
       </c>
@@ -18132,7 +19334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A297" s="21">
         <v>43659</v>
       </c>
@@ -18191,7 +19393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A298" s="21">
         <v>43659</v>
       </c>
@@ -18250,7 +19452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A299" s="21">
         <v>43659</v>
       </c>
@@ -18309,7 +19511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A300" s="21">
         <v>43659</v>
       </c>
@@ -18368,7 +19570,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A301" s="21">
         <v>43659</v>
       </c>
@@ -18427,7 +19629,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A302" s="21">
         <v>43659</v>
       </c>
@@ -18486,7 +19688,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="303" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A303" s="21">
         <v>43659</v>
       </c>
@@ -18545,7 +19747,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="304" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A304" s="21">
         <v>43659</v>
       </c>
@@ -18604,7 +19806,7 @@
         <v>97.9</v>
       </c>
     </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A305" s="21">
         <v>43659</v>
       </c>
@@ -18663,7 +19865,7 @@
         <v>141.5</v>
       </c>
     </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A306" s="21">
         <v>43659</v>
       </c>
@@ -18722,7 +19924,7 @@
         <v>116.09999999999998</v>
       </c>
     </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A307" s="21">
         <v>43659</v>
       </c>
@@ -18781,7 +19983,7 @@
         <v>210.4</v>
       </c>
     </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A308" s="21">
         <v>43659</v>
       </c>
@@ -18840,7 +20042,7 @@
         <v>174.1</v>
       </c>
     </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A309" s="21">
         <v>43659</v>
       </c>
@@ -18899,7 +20101,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A310" s="21">
         <v>43659</v>
       </c>
@@ -18958,7 +20160,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A311" s="21">
         <v>43659</v>
       </c>
@@ -19017,7 +20219,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A312" s="21">
         <v>43659</v>
       </c>
@@ -19076,7 +20278,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A313" s="21">
         <v>43659</v>
       </c>
@@ -19135,7 +20337,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A314" s="21">
         <v>43659</v>
       </c>
@@ -19194,7 +20396,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="315" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A315" s="21">
         <v>43659</v>
       </c>
@@ -19253,7 +20455,7 @@
         <v>134.19999999999999</v>
       </c>
     </row>
-    <row r="316" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A316" s="21">
         <v>43659</v>
       </c>
@@ -19312,7 +20514,7 @@
         <v>335.5</v>
       </c>
     </row>
-    <row r="317" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A317" s="21">
         <v>43659</v>
       </c>
@@ -19371,7 +20573,7 @@
         <v>117.89999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A318" s="21">
         <v>43659</v>
       </c>
@@ -19430,7 +20632,7 @@
         <v>76.2</v>
       </c>
     </row>
-    <row r="319" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A319" s="21">
         <v>43659</v>
       </c>
@@ -19489,7 +20691,7 @@
         <v>79.8</v>
       </c>
     </row>
-    <row r="320" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A320" s="21">
         <v>43659</v>
       </c>
@@ -19548,7 +20750,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A321" s="21">
         <v>43659</v>
       </c>
@@ -19607,7 +20809,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="322" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A322" s="21">
         <v>43659</v>
       </c>
@@ -19666,7 +20868,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A323" s="21">
         <v>43659</v>
       </c>
@@ -19725,7 +20927,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A324" s="21">
         <v>43659</v>
       </c>
@@ -19784,7 +20986,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A325" s="21">
         <v>43659</v>
       </c>
@@ -19843,7 +21045,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A326" s="21">
         <v>43659</v>
       </c>
@@ -19902,7 +21104,7 @@
         <v>27.199999999999996</v>
       </c>
     </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A327" s="21">
         <v>43659</v>
       </c>
@@ -19961,7 +21163,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A328" s="21">
         <v>43659</v>
       </c>
@@ -20020,7 +21222,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A329" s="21">
         <v>43659</v>
       </c>
@@ -20079,7 +21281,7 @@
         <v>7.2999999999999989</v>
       </c>
     </row>
-    <row r="330" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A330" s="21">
         <v>43659</v>
       </c>
@@ -20138,7 +21340,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="331" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A331" s="21">
         <v>43659</v>
       </c>
@@ -20197,7 +21399,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A332" s="21">
         <v>43659</v>
       </c>
@@ -20256,7 +21458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A333" s="21">
         <v>43659</v>
       </c>
@@ -20315,7 +21517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A334" s="21">
         <v>43659</v>
       </c>
@@ -20374,7 +21576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A335" s="21">
         <v>43659</v>
       </c>
@@ -20433,7 +21635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A336" s="21">
         <v>43659</v>
       </c>
@@ -20492,7 +21694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A337" s="21">
         <v>43659</v>
       </c>
@@ -20551,7 +21753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A338" s="21">
         <v>43659</v>
       </c>
@@ -20610,7 +21812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A339" s="21">
         <v>43659</v>
       </c>
@@ -20669,7 +21871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A340" s="21">
         <v>43660</v>
       </c>
@@ -20728,7 +21930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A341" s="21">
         <v>43660</v>
       </c>
@@ -20787,7 +21989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A342" s="21">
         <v>43660</v>
       </c>
@@ -20846,7 +22048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A343" s="21">
         <v>43660</v>
       </c>
@@ -20905,7 +22107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A344" s="21">
         <v>43660</v>
       </c>
@@ -20964,7 +22166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A345" s="21">
         <v>43660</v>
       </c>
@@ -21023,7 +22225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A346" s="21">
         <v>43660</v>
       </c>
@@ -21082,7 +22284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A347" s="21">
         <v>43660</v>
       </c>
@@ -21141,7 +22343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A348" s="21">
         <v>43660</v>
       </c>
@@ -21200,7 +22402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A349" s="21">
         <v>43660</v>
       </c>
@@ -21259,7 +22461,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A350" s="21">
         <v>43660</v>
       </c>
@@ -21318,7 +22520,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A351" s="21">
         <v>43660</v>
       </c>
@@ -21377,7 +22579,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A352" s="21">
         <v>43660</v>
       </c>
@@ -21436,7 +22638,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A353" s="21">
         <v>43660</v>
       </c>
@@ -21495,7 +22697,7 @@
         <v>59.9</v>
       </c>
     </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A354" s="21">
         <v>43660</v>
       </c>
@@ -21554,7 +22756,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A355" s="21">
         <v>43660</v>
       </c>
@@ -21613,7 +22815,7 @@
         <v>132.4</v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A356" s="21">
         <v>43660</v>
       </c>
@@ -21672,7 +22874,7 @@
         <v>141.5</v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A357" s="21">
         <v>43660</v>
       </c>
@@ -21731,7 +22933,7 @@
         <v>208.60000000000002</v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A358" s="21">
         <v>43660</v>
       </c>
@@ -21790,7 +22992,7 @@
         <v>297.39999999999998</v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A359" s="21">
         <v>43660</v>
       </c>
@@ -21849,7 +23051,7 @@
         <v>112.4</v>
       </c>
     </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A360" s="21">
         <v>43660</v>
       </c>
@@ -21908,7 +23110,7 @@
         <v>163.19999999999999</v>
       </c>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A361" s="21">
         <v>43660</v>
       </c>
@@ -21967,7 +23169,7 @@
         <v>237.6</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A362" s="21">
         <v>43660</v>
       </c>
@@ -22026,7 +23228,7 @@
         <v>235.8</v>
       </c>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A363" s="21">
         <v>43660</v>
       </c>
@@ -22085,7 +23287,7 @@
         <v>244.8</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A364" s="21">
         <v>43660</v>
       </c>
@@ -22144,7 +23346,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A365" s="21">
         <v>43660</v>
       </c>
@@ -22203,7 +23405,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A366" s="21">
         <v>43660</v>
       </c>
@@ -22262,7 +23464,7 @@
         <v>183.2</v>
       </c>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A367" s="21">
         <v>43660</v>
       </c>
@@ -22321,7 +23523,7 @@
         <v>273.89999999999998</v>
       </c>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A368" s="21">
         <v>43660</v>
       </c>
@@ -22380,7 +23582,7 @@
         <v>264.8</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A369" s="21">
         <v>43660</v>
       </c>
@@ -22439,7 +23641,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A370" s="21">
         <v>43660</v>
       </c>
@@ -22498,7 +23700,7 @@
         <v>331.9</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A371" s="21">
         <v>43660</v>
       </c>
@@ -22557,7 +23759,7 @@
         <v>175.9</v>
       </c>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A372" s="21">
         <v>43660</v>
       </c>
@@ -22616,7 +23818,7 @@
         <v>224.9</v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A373" s="21">
         <v>43660</v>
       </c>
@@ -22675,7 +23877,7 @@
         <v>150.5</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A374" s="21">
         <v>43660</v>
       </c>
@@ -22734,7 +23936,7 @@
         <v>130.6</v>
       </c>
     </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A375" s="21">
         <v>43660</v>
       </c>
@@ -22793,7 +23995,7 @@
         <v>119.7</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A376" s="21">
         <v>43660</v>
       </c>
@@ -22852,7 +24054,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A377" s="21">
         <v>43660</v>
       </c>
@@ -22911,7 +24113,7 @@
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A378" s="21">
         <v>43660</v>
       </c>
@@ -22970,7 +24172,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A379" s="21">
         <v>43660</v>
       </c>
@@ -23029,7 +24231,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A380" s="21">
         <v>43660</v>
       </c>
@@ -23088,7 +24290,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A381" s="21">
         <v>43660</v>
       </c>
@@ -23147,7 +24349,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A382" s="21">
         <v>43660</v>
       </c>
@@ -23206,7 +24408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A383" s="21">
         <v>43660</v>
       </c>
@@ -23265,7 +24467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A384" s="21">
         <v>43660</v>
       </c>
@@ -23324,7 +24526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A385" s="21">
         <v>43660</v>
       </c>
@@ -23383,7 +24585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A386" s="21">
         <v>43660</v>
       </c>
@@ -23442,7 +24644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A387" s="21">
         <v>43660</v>
       </c>
@@ -23501,7 +24703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A388" s="21">
         <v>43661</v>
       </c>
@@ -23560,7 +24762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A389" s="21">
         <v>43661</v>
       </c>
@@ -23619,7 +24821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A390" s="21">
         <v>43661</v>
       </c>
@@ -23678,7 +24880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A391" s="21">
         <v>43661</v>
       </c>
@@ -23737,7 +24939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A392" s="21">
         <v>43661</v>
       </c>
@@ -23796,7 +24998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A393" s="21">
         <v>43661</v>
       </c>
@@ -23855,7 +25057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A394" s="21">
         <v>43661</v>
       </c>
@@ -23914,7 +25116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A395" s="21">
         <v>43661</v>
       </c>
@@ -23973,7 +25175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A396" s="21">
         <v>43661</v>
       </c>
@@ -24032,7 +25234,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A397" s="21">
         <v>43661</v>
       </c>
@@ -24091,7 +25293,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A398" s="21">
         <v>43661</v>
       </c>
@@ -24150,7 +25352,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A399" s="21">
         <v>43661</v>
       </c>
@@ -24209,7 +25411,7 @@
         <v>195.9</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A400" s="21">
         <v>43661</v>
       </c>
@@ -24268,7 +25470,7 @@
         <v>70.7</v>
       </c>
     </row>
-    <row r="401" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A401" s="21">
         <v>43661</v>
       </c>
@@ -24327,7 +25529,7 @@
         <v>301.10000000000002</v>
       </c>
     </row>
-    <row r="402" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A402" s="21">
         <v>43661</v>
       </c>
@@ -24386,7 +25588,7 @@
         <v>342.8</v>
       </c>
     </row>
-    <row r="403" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A403" s="21">
         <v>43661</v>
       </c>
@@ -24445,7 +25647,7 @@
         <v>438.9</v>
       </c>
     </row>
-    <row r="404" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A404" s="21">
         <v>43661</v>
       </c>
@@ -24504,7 +25706,7 @@
         <v>533.20000000000005</v>
       </c>
     </row>
-    <row r="405" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A405" s="21">
         <v>43661</v>
       </c>
@@ -24563,7 +25765,7 @@
         <v>600.29999999999995</v>
       </c>
     </row>
-    <row r="406" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A406" s="21">
         <v>43661</v>
       </c>
@@ -24622,7 +25824,7 @@
         <v>667.4</v>
       </c>
     </row>
-    <row r="407" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A407" s="21">
         <v>43661</v>
       </c>
@@ -24681,7 +25883,7 @@
         <v>712.8</v>
       </c>
     </row>
-    <row r="408" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A408" s="21">
         <v>43661</v>
       </c>
@@ -24740,7 +25942,7 @@
         <v>783.5</v>
       </c>
     </row>
-    <row r="409" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A409" s="21">
         <v>43661</v>
       </c>
@@ -24799,7 +26001,7 @@
         <v>729.09999999999991</v>
       </c>
     </row>
-    <row r="410" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A410" s="21">
         <v>43661</v>
       </c>
@@ -24858,7 +26060,7 @@
         <v>866.9</v>
       </c>
     </row>
-    <row r="411" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A411" s="21">
         <v>43661</v>
       </c>
@@ -24917,7 +26119,7 @@
         <v>204.9</v>
       </c>
     </row>
-    <row r="412" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A412" s="21">
         <v>43661</v>
       </c>
@@ -24976,7 +26178,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="413" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A413" s="21">
         <v>43661</v>
       </c>
@@ -25035,7 +26237,7 @@
         <v>224.89999999999998</v>
       </c>
     </row>
-    <row r="414" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A414" s="21">
         <v>43661</v>
       </c>
@@ -25094,7 +26296,7 @@
         <v>237.6</v>
       </c>
     </row>
-    <row r="415" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A415" s="21">
         <v>43661</v>
       </c>
@@ -25153,7 +26355,7 @@
         <v>282.89999999999998</v>
       </c>
     </row>
-    <row r="416" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A416" s="21">
         <v>43661</v>
       </c>
@@ -25212,7 +26414,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="417" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A417" s="21">
         <v>43661</v>
       </c>
@@ -25271,7 +26473,7 @@
         <v>103.4</v>
       </c>
     </row>
-    <row r="418" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A418" s="21">
         <v>43661</v>
       </c>
@@ -25330,7 +26532,7 @@
         <v>161.4</v>
       </c>
     </row>
-    <row r="419" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A419" s="21">
         <v>43661</v>
       </c>
@@ -25389,7 +26591,7 @@
         <v>228.5</v>
       </c>
     </row>
-    <row r="420" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A420" s="21">
         <v>43661</v>
       </c>
@@ -25448,7 +26650,7 @@
         <v>108.8</v>
       </c>
     </row>
-    <row r="421" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A421" s="21">
         <v>43661</v>
       </c>
@@ -25507,7 +26709,7 @@
         <v>96.1</v>
       </c>
     </row>
-    <row r="422" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A422" s="21">
         <v>43661</v>
       </c>
@@ -25566,7 +26768,7 @@
         <v>94.3</v>
       </c>
     </row>
-    <row r="423" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A423" s="21">
         <v>43661</v>
       </c>
@@ -25625,7 +26827,7 @@
         <v>152.29999999999998</v>
       </c>
     </row>
-    <row r="424" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A424" s="21">
         <v>43661</v>
       </c>
@@ -25684,7 +26886,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="425" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A425" s="21">
         <v>43661</v>
       </c>
@@ -25743,7 +26945,7 @@
         <v>30.800000000000004</v>
       </c>
     </row>
-    <row r="426" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A426" s="21">
         <v>43661</v>
       </c>
@@ -25802,7 +27004,7 @@
         <v>21.800000000000004</v>
       </c>
     </row>
-    <row r="427" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A427" s="21">
         <v>43661</v>
       </c>
@@ -25861,7 +27063,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="428" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A428" s="21">
         <v>43661</v>
       </c>
@@ -25920,7 +27122,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="429" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A429" s="21">
         <v>43661</v>
       </c>
@@ -25979,7 +27181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A430" s="21">
         <v>43661</v>
       </c>
@@ -26038,7 +27240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A431" s="21">
         <v>43661</v>
       </c>
@@ -26097,7 +27299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A432" s="21">
         <v>43661</v>
       </c>
@@ -26156,7 +27358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A433" s="21">
         <v>43661</v>
       </c>
@@ -26215,7 +27417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A434" s="21">
         <v>43661</v>
       </c>
@@ -26274,7 +27476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A435" s="21">
         <v>43661</v>
       </c>
@@ -26333,7 +27535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A436" s="21">
         <v>43662</v>
       </c>
@@ -26392,7 +27594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A437" s="21">
         <v>43662</v>
       </c>
@@ -26451,7 +27653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A438" s="21">
         <v>43662</v>
       </c>
@@ -26510,7 +27712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A439" s="21">
         <v>43662</v>
       </c>
@@ -26569,7 +27771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A440" s="21">
         <v>43662</v>
       </c>
@@ -26628,7 +27830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A441" s="21">
         <v>43662</v>
       </c>
@@ -26687,7 +27889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A442" s="21">
         <v>43662</v>
       </c>
@@ -26746,7 +27948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A443" s="21">
         <v>43662</v>
       </c>
@@ -26805,7 +28007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A444" s="21">
         <v>43662</v>
       </c>
@@ -26864,7 +28066,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="445" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A445" s="21">
         <v>43662</v>
       </c>
@@ -26923,7 +28125,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="446" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A446" s="21">
         <v>43662</v>
       </c>
@@ -26982,7 +28184,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="447" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A447" s="21">
         <v>43662</v>
       </c>
@@ -27041,7 +28243,7 @@
         <v>145.1</v>
       </c>
     </row>
-    <row r="448" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A448" s="21">
         <v>43662</v>
       </c>
@@ -27100,7 +28302,7 @@
         <v>223.1</v>
       </c>
     </row>
-    <row r="449" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A449" s="21">
         <v>43662</v>
       </c>
@@ -27159,7 +28361,7 @@
         <v>295.60000000000002</v>
       </c>
     </row>
-    <row r="450" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A450" s="21">
         <v>43662</v>
       </c>
@@ -27218,7 +28420,7 @@
         <v>359.1</v>
       </c>
     </row>
-    <row r="451" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A451" s="21">
         <v>43662</v>
       </c>
@@ -27277,7 +28479,7 @@
         <v>440.7</v>
       </c>
     </row>
-    <row r="452" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A452" s="21">
         <v>43662</v>
       </c>
@@ -27336,7 +28538,7 @@
         <v>516.9</v>
       </c>
     </row>
-    <row r="453" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A453" s="21">
         <v>43662</v>
       </c>
@@ -27395,7 +28597,7 @@
         <v>582.20000000000005</v>
       </c>
     </row>
-    <row r="454" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A454" s="21">
         <v>43662</v>
       </c>
@@ -27454,7 +28656,7 @@
         <v>651.1</v>
       </c>
     </row>
-    <row r="455" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A455" s="21">
         <v>43662</v>
       </c>
@@ -27513,7 +28715,7 @@
         <v>709.1</v>
       </c>
     </row>
-    <row r="456" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A456" s="21">
         <v>43662</v>
       </c>
@@ -27572,7 +28774,7 @@
         <v>828.8</v>
       </c>
     </row>
-    <row r="457" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A457" s="21">
         <v>43662</v>
       </c>
@@ -27631,7 +28833,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="458" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A458" s="21">
         <v>43662</v>
       </c>
@@ -27690,7 +28892,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="459" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A459" s="21">
         <v>43662</v>
       </c>
@@ -27749,7 +28951,7 @@
         <v>331.9</v>
       </c>
     </row>
-    <row r="460" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A460" s="21">
         <v>43662</v>
       </c>
@@ -27808,7 +29010,7 @@
         <v>208.6</v>
       </c>
     </row>
-    <row r="461" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A461" s="21">
         <v>43662</v>
       </c>
@@ -27867,7 +29069,7 @@
         <v>114.29999999999998</v>
       </c>
     </row>
-    <row r="462" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A462" s="21">
         <v>43662</v>
       </c>
@@ -27926,7 +29128,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="463" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A463" s="21">
         <v>43662</v>
       </c>
@@ -27985,7 +29187,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="464" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A464" s="21">
         <v>43662</v>
       </c>
@@ -28044,7 +29246,7 @@
         <v>59.900000000000006</v>
       </c>
     </row>
-    <row r="465" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A465" s="21">
         <v>43662</v>
       </c>
@@ -28103,7 +29305,7 @@
         <v>157.80000000000001</v>
       </c>
     </row>
-    <row r="466" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A466" s="21">
         <v>43662</v>
       </c>
@@ -28162,7 +29364,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="467" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A467" s="21">
         <v>43662</v>
       </c>
@@ -28221,7 +29423,7 @@
         <v>194.1</v>
       </c>
     </row>
-    <row r="468" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A468" s="21">
         <v>43662</v>
       </c>
@@ -28280,7 +29482,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="469" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A469" s="21">
         <v>43662</v>
       </c>
@@ -28339,7 +29541,7 @@
         <v>246.69999999999996</v>
       </c>
     </row>
-    <row r="470" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A470" s="21">
         <v>43662</v>
       </c>
@@ -28398,7 +29600,7 @@
         <v>190.4</v>
       </c>
     </row>
-    <row r="471" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A471" s="21">
         <v>43662</v>
       </c>
@@ -28457,7 +29659,7 @@
         <v>125.1</v>
       </c>
     </row>
-    <row r="472" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A472" s="21">
         <v>43662</v>
       </c>
@@ -28516,7 +29718,7 @@
         <v>119.7</v>
       </c>
     </row>
-    <row r="473" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A473" s="21">
         <v>43662</v>
       </c>
@@ -28575,7 +29777,7 @@
         <v>54.4</v>
       </c>
     </row>
-    <row r="474" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A474" s="21">
         <v>43662</v>
       </c>
@@ -28634,7 +29836,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="475" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A475" s="21">
         <v>43662</v>
       </c>
@@ -28693,7 +29895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A476" s="21">
         <v>43662</v>
       </c>
@@ -28752,7 +29954,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="477" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A477" s="21">
         <v>43662</v>
       </c>
@@ -28811,7 +30013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A478" s="21">
         <v>43662</v>
       </c>
@@ -28870,7 +30072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A479" s="21">
         <v>43662</v>
       </c>
@@ -28929,7 +30131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A480" s="21">
         <v>43662</v>
       </c>
@@ -28988,7 +30190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A481" s="21">
         <v>43662</v>
       </c>
@@ -29047,7 +30249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A482" s="21">
         <v>43662</v>
       </c>
@@ -29106,7 +30308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A483" s="21">
         <v>43662</v>
       </c>
@@ -29168,4 +30370,399 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4FCDD80-E284-4268-8158-898E0F3995CE}">
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="7">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>13.8429</v>
+      </c>
+      <c r="B8">
+        <v>13.84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>24.434699999999999</v>
+      </c>
+      <c r="B9">
+        <v>24.43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>35.100700000000003</v>
+      </c>
+      <c r="B10">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>45.506999999999998</v>
+      </c>
+      <c r="B11">
+        <v>45.51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>32.2926</v>
+      </c>
+      <c r="B12">
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>80.984499999999997</v>
+      </c>
+      <c r="B13">
+        <v>80.98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>139.16999999999999</v>
+      </c>
+      <c r="B14">
+        <v>139.16999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>204.679</v>
+      </c>
+      <c r="B15">
+        <v>204.68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>275.43900000000002</v>
+      </c>
+      <c r="B16">
+        <v>275.44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>349.464</v>
+      </c>
+      <c r="B17">
+        <v>349.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>424.86599999999999</v>
+      </c>
+      <c r="B18">
+        <v>424.87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>499.86200000000002</v>
+      </c>
+      <c r="B19">
+        <v>499.86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>572.779</v>
+      </c>
+      <c r="B20">
+        <v>572.78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>642.06600000000003</v>
+      </c>
+      <c r="B21">
+        <v>642.07000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>706.298</v>
+      </c>
+      <c r="B22">
+        <v>706.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>764.17499999999995</v>
+      </c>
+      <c r="B23">
+        <v>764.18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>814.53200000000004</v>
+      </c>
+      <c r="B24">
+        <v>814.53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>856.33399999999995</v>
+      </c>
+      <c r="B25">
+        <v>856.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>888.68799999999999</v>
+      </c>
+      <c r="B26">
+        <v>888.69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>910.83799999999997</v>
+      </c>
+      <c r="B27">
+        <v>910.84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>922.18</v>
+      </c>
+      <c r="B28">
+        <v>922.18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>922.26400000000001</v>
+      </c>
+      <c r="B29">
+        <v>922.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>910.80700000000002</v>
+      </c>
+      <c r="B30">
+        <v>910.81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>887.70500000000004</v>
+      </c>
+      <c r="B31">
+        <v>887.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>853.048</v>
+      </c>
+      <c r="B32">
+        <v>853.05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>807.13699999999994</v>
+      </c>
+      <c r="B33">
+        <v>807.14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>750.49800000000005</v>
+      </c>
+      <c r="B34">
+        <v>750.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>683.90099999999995</v>
+      </c>
+      <c r="B35">
+        <v>683.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>608.38099999999997</v>
+      </c>
+      <c r="B36">
+        <v>608.38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>64.416799999999995</v>
+      </c>
+      <c r="B37">
+        <v>64.42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>55.3596</v>
+      </c>
+      <c r="B38">
+        <v>55.36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
+        <v>45.506999999999998</v>
+      </c>
+      <c r="B39">
+        <v>45.51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>35.100700000000003</v>
+      </c>
+      <c r="B40">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>24.434699999999999</v>
+      </c>
+      <c r="B41">
+        <v>24.43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>13.8429</v>
+      </c>
+      <c r="B42">
+        <v>13.84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>0</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>0</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>0</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>0</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>0</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>0</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/ячейка96(10 дней).xlsx
+++ b/ячейка96(10 дней).xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skibc\PycharmProjects\ZORIN grass 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED56A54D-B4DA-4A41-82E1-8408ACEF157F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD828A00-4FD9-4373-AA53-34BA7D6A9D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3825" yWindow="3285" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{41652E5A-C04B-41B8-B8AF-E4D3B08BB20D}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14505" windowHeight="15585" activeTab="2" xr2:uid="{41652E5A-C04B-41B8-B8AF-E4D3B08BB20D}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -402,6 +403,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>r</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> sun</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -988,6 +1019,3225 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>sin cell 10 days</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист3!$A$1:$A$480</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="480"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>145.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>230.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>295.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>382.7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>455.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>516.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>589.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>658.4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>711</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>783.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>912.3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>890.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>981.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>955.8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1026.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>714.6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>281.10000000000002</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>272.10000000000002</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>224.9</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>252.1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>382.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>275.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>110.6</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>101.6</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>72.5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>110.6</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>186.8</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>183.2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>110.6</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>235.8</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>170.5</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>175.9</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>341</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>558.6</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>480.6</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>52.6</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>235.8</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>152.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>141.5</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>88.9</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>43.5</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>119.7</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>88.9</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>132.4</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>154.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>382.7</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>94.3</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>63.5</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>79.8</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>88.9</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>65.3</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>63.5</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>16.3</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>116.1</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>175.9</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>295.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>366.4</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>444.4</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>527.79999999999995</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>594.9</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>663.8</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>721.8</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>787.1</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>839.7</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>877.8</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>228.5</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>253.9</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>179.6</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>121.5</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>181.4</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>152.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>348.2</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>219.5</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>161.4</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>275.7</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>45.3</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>70.7</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>117.9</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>195.9</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>154.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>145.1</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>192.2</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>166.9</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>208.6</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>228.5</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>279.3</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>266.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>192.2</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>284.7</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>186.8</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>177.7</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>192.2</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>137.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>219.5</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>190.4</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>188.6</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>210.4</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>137.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>39.9</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>16.3</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>342.8</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>59.9</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>466.1</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>515.1</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>288.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>47.2</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>295.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>478.8</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>886.9</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>183.2</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>97.9</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>99.8</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>301.10000000000002</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>1024.7</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>674.7</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>923.2</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>65.3</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>76.2</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>72.5</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>50.8</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>108.8</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>63.5</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>47.2</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>36.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>56.2</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>97.9</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>141.5</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>116.1</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>210.4</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>174.1</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>92.5</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>63.5</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>45.3</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>92.5</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>134.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>335.5</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>117.9</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>76.2</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>79.8</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>43.5</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>43.5</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>65.3</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>23.6</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>41.7</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>16.3</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>59.9</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>92.5</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>132.4</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>141.5</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>208.6</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>297.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>112.4</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>163.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>237.6</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>235.8</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>244.8</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>183.2</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>273.89999999999998</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>264.8</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>331.9</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>175.9</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>224.9</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>150.5</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>130.6</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>119.7</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>74.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>39.9</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>195.9</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>70.7</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>301.10000000000002</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>342.8</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>438.9</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>533.20000000000005</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>600.29999999999995</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>667.4</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>712.8</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>783.5</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>729.1</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>866.9</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>204.9</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>896</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>224.9</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>237.6</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>282.89999999999998</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>103.4</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>161.4</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>228.5</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>108.8</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>96.1</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>94.3</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>152.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>39.9</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>145.1</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>223.1</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>295.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>359.1</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>440.7</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>516.9</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>582.20000000000005</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>651.1</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>709.1</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>828.8</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>331.9</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>208.6</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>114.3</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>47.2</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>59.9</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>157.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>194.1</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>312</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>246.7</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>190.4</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>125.1</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>119.7</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>54.4</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B0BA-41E0-8E44-3F203B4985CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист3!$B$1:$B$480</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="480"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>145.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>230.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>295.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>382.7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>455.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>516.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>589.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>658.4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>711</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>783.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>912.3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>890.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>981.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>955.8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1026.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>714.6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>281.10000000000002</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>272.10000000000002</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>224.9</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>252.1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>382.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>275.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>110.6</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>101.6</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>72.5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>110.6</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>186.8</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>183.2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>110.6</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>235.8</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>170.5</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>175.9</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>341</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>558.6</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>480.6</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>52.6</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>235.8</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>152.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>141.5</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>88.9</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>43.5</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>119.7</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>88.9</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>132.4</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>154.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>382.7</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>94.3</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>63.5</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>79.8</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>88.9</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>65.3</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>63.5</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>16.3</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>116.1</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>175.9</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>295.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>366.4</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>444.4</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>527.79999999999995</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>594.9</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>663.8</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>721.8</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>787.1</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>839.7</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>877.8</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>228.5</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>253.9</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>179.6</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>121.5</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>181.4</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>152.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>348.2</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>219.5</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>161.4</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>275.7</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>45.3</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>70.7</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>117.9</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>195.9</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>154.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>145.1</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>192.2</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>166.9</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>208.6</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>228.5</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>279.3</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>266.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>192.2</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>284.7</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>186.8</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>177.7</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>192.2</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>137.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>219.5</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>190.4</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>188.6</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>210.4</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>137.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>39.9</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>16.3</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>342.8</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>59.9</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>466.1</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>515.1</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>288.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>47.2</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>295.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>478.8</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>886.9</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>183.2</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>97.9</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>99.8</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>301.10000000000002</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>1024.7</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>674.7</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>923.2</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>65.3</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>76.2</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>72.5</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>50.8</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>108.8</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>63.5</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>47.2</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>36.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>56.2</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>97.9</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>141.5</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>116.1</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>210.4</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>174.1</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>92.5</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>63.5</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>45.3</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>92.5</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>134.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>335.5</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>117.9</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>76.2</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>79.8</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>43.5</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>43.5</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>65.3</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>23.6</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>41.7</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>16.3</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>59.9</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>92.5</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>132.4</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>141.5</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>208.6</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>297.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>112.4</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>163.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>237.6</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>235.8</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>244.8</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>183.2</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>273.89999999999998</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>264.8</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>331.9</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>175.9</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>224.9</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>150.5</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>130.6</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>119.7</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>74.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>39.9</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>27.2</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>195.9</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>70.7</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>301.10000000000002</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>342.8</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>438.9</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>533.20000000000005</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>600.29999999999995</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>667.4</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>712.8</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>783.5</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>729.1</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>866.9</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>204.9</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>896</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>224.9</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>237.6</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>282.89999999999998</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>277.5</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>103.4</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>161.4</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>228.5</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>108.8</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>96.1</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>94.3</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>152.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>39.9</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>145.1</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>223.1</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>295.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>359.1</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>440.7</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>516.9</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>582.20000000000005</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>651.1</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>709.1</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>828.8</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>331.9</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>208.6</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>114.3</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>47.2</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>59.9</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>157.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>194.1</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>312</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>246.7</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>190.4</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>125.1</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>119.7</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>54.4</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B0BA-41E0-8E44-3F203B4985CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="773967152"/>
+        <c:axId val="773976272"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="773967152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="773976272"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="773976272"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="773967152"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1028,7 +4278,563 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1585,6 +5391,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>185737</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>421821</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>138112</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE55D620-D577-277F-10F3-B07F18B9854C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
@@ -30765,4 +34612,3855 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D2ED251-26C6-4CE5-9A80-CC6D192D4B50}">
+  <dimension ref="A1:B480"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>0</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>0</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>0</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>0</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="B9" s="9">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>21.8</v>
+      </c>
+      <c r="B10" s="9">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="B11" s="9">
+        <v>81.599999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>145.1</v>
+      </c>
+      <c r="B12" s="9">
+        <v>145.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
+        <v>230.3</v>
+      </c>
+      <c r="B13" s="9">
+        <v>230.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>295.60000000000002</v>
+      </c>
+      <c r="B14" s="9">
+        <v>295.60000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>382.7</v>
+      </c>
+      <c r="B15" s="9">
+        <v>382.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
+        <v>455.2</v>
+      </c>
+      <c r="B16" s="9">
+        <v>455.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>516.9</v>
+      </c>
+      <c r="B17" s="9">
+        <v>516.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>589.4</v>
+      </c>
+      <c r="B18" s="9">
+        <v>589.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>658.4</v>
+      </c>
+      <c r="B19" s="9">
+        <v>658.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>711</v>
+      </c>
+      <c r="B20" s="9">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>783.5</v>
+      </c>
+      <c r="B21" s="9">
+        <v>783.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
+        <v>912.3</v>
+      </c>
+      <c r="B22" s="9">
+        <v>912.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>890.5</v>
+      </c>
+      <c r="B23" s="9">
+        <v>890.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
+        <v>981.2</v>
+      </c>
+      <c r="B24" s="9">
+        <v>981.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>955.8</v>
+      </c>
+      <c r="B25" s="9">
+        <v>955.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>1026.5</v>
+      </c>
+      <c r="B26" s="9">
+        <v>1026.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>350</v>
+      </c>
+      <c r="B27" s="9">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>714.6</v>
+      </c>
+      <c r="B28" s="9">
+        <v>714.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>281.10000000000002</v>
+      </c>
+      <c r="B29" s="9">
+        <v>281.10000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>272.10000000000002</v>
+      </c>
+      <c r="B30" s="9">
+        <v>272.10000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
+        <v>224.9</v>
+      </c>
+      <c r="B31" s="9">
+        <v>224.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="9">
+        <v>252.1</v>
+      </c>
+      <c r="B32" s="9">
+        <v>252.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="9">
+        <v>382.7</v>
+      </c>
+      <c r="B33" s="9">
+        <v>382.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="9">
+        <v>275.7</v>
+      </c>
+      <c r="B34" s="9">
+        <v>275.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="9">
+        <v>214</v>
+      </c>
+      <c r="B35" s="9">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="9">
+        <v>110.6</v>
+      </c>
+      <c r="B36" s="9">
+        <v>110.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="9">
+        <v>101.6</v>
+      </c>
+      <c r="B37" s="9">
+        <v>101.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="9">
+        <v>72.5</v>
+      </c>
+      <c r="B38" s="9">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="9">
+        <v>49</v>
+      </c>
+      <c r="B39" s="9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="9">
+        <v>34.5</v>
+      </c>
+      <c r="B40" s="9">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="9">
+        <v>25.4</v>
+      </c>
+      <c r="B41" s="9">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="B42" s="9">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="9">
+        <v>0</v>
+      </c>
+      <c r="B43" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="9">
+        <v>0</v>
+      </c>
+      <c r="B44" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="9">
+        <v>0</v>
+      </c>
+      <c r="B45" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="9">
+        <v>0</v>
+      </c>
+      <c r="B46" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="9">
+        <v>0</v>
+      </c>
+      <c r="B47" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="9">
+        <v>0</v>
+      </c>
+      <c r="B48" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="9">
+        <v>0</v>
+      </c>
+      <c r="B49" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="9">
+        <v>0</v>
+      </c>
+      <c r="B50" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="9">
+        <v>0</v>
+      </c>
+      <c r="B51" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="9">
+        <v>0</v>
+      </c>
+      <c r="B52" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="9">
+        <v>0</v>
+      </c>
+      <c r="B53" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="9">
+        <v>0</v>
+      </c>
+      <c r="B54" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="9">
+        <v>0</v>
+      </c>
+      <c r="B55" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="9">
+        <v>0</v>
+      </c>
+      <c r="B56" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="9">
+        <v>0</v>
+      </c>
+      <c r="B57" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="B58" s="9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="9">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="B59" s="9">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="9">
+        <v>34.5</v>
+      </c>
+      <c r="B60" s="9">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="9">
+        <v>49</v>
+      </c>
+      <c r="B61" s="9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="9">
+        <v>110.6</v>
+      </c>
+      <c r="B62" s="9">
+        <v>110.6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="9">
+        <v>186.8</v>
+      </c>
+      <c r="B63" s="9">
+        <v>186.8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="9">
+        <v>183.2</v>
+      </c>
+      <c r="B64" s="9">
+        <v>183.2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="9">
+        <v>110.6</v>
+      </c>
+      <c r="B65" s="9">
+        <v>110.6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="9">
+        <v>277.5</v>
+      </c>
+      <c r="B66" s="9">
+        <v>277.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="9">
+        <v>235.8</v>
+      </c>
+      <c r="B67" s="9">
+        <v>235.8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="9">
+        <v>170.5</v>
+      </c>
+      <c r="B68" s="9">
+        <v>170.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="9">
+        <v>175.9</v>
+      </c>
+      <c r="B69" s="9">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="9">
+        <v>341</v>
+      </c>
+      <c r="B70" s="9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="9">
+        <v>558.6</v>
+      </c>
+      <c r="B71" s="9">
+        <v>558.6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="9">
+        <v>480.6</v>
+      </c>
+      <c r="B72" s="9">
+        <v>480.6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="9">
+        <v>27.2</v>
+      </c>
+      <c r="B73" s="9">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="9">
+        <v>25.4</v>
+      </c>
+      <c r="B74" s="9">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="9">
+        <v>27.2</v>
+      </c>
+      <c r="B75" s="9">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="9">
+        <v>29</v>
+      </c>
+      <c r="B76" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="9">
+        <v>29</v>
+      </c>
+      <c r="B77" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="9">
+        <v>34.5</v>
+      </c>
+      <c r="B78" s="9">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="9">
+        <v>52.6</v>
+      </c>
+      <c r="B79" s="9">
+        <v>52.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="9">
+        <v>235.8</v>
+      </c>
+      <c r="B80" s="9">
+        <v>235.8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="9">
+        <v>248.5</v>
+      </c>
+      <c r="B81" s="9">
+        <v>248.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="9">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="B82" s="9">
+        <v>152.30000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="9">
+        <v>165</v>
+      </c>
+      <c r="B83" s="9">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="9">
+        <v>141.5</v>
+      </c>
+      <c r="B84" s="9">
+        <v>141.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="9">
+        <v>88.9</v>
+      </c>
+      <c r="B85" s="9">
+        <v>88.9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="9">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="B86" s="9">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="9">
+        <v>10.9</v>
+      </c>
+      <c r="B87" s="9">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="B88" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="9">
+        <v>0</v>
+      </c>
+      <c r="B89" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="9">
+        <v>0</v>
+      </c>
+      <c r="B90" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="9">
+        <v>0</v>
+      </c>
+      <c r="B91" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="9">
+        <v>0</v>
+      </c>
+      <c r="B92" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="9">
+        <v>0</v>
+      </c>
+      <c r="B93" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="9">
+        <v>0</v>
+      </c>
+      <c r="B94" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="9">
+        <v>0</v>
+      </c>
+      <c r="B95" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="9">
+        <v>0</v>
+      </c>
+      <c r="B96" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="9">
+        <v>0</v>
+      </c>
+      <c r="B97" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="9">
+        <v>0</v>
+      </c>
+      <c r="B98" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="9">
+        <v>0</v>
+      </c>
+      <c r="B99" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="9">
+        <v>0</v>
+      </c>
+      <c r="B100" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="9">
+        <v>0</v>
+      </c>
+      <c r="B101" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="9">
+        <v>0</v>
+      </c>
+      <c r="B102" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="9">
+        <v>0</v>
+      </c>
+      <c r="B103" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="9">
+        <v>0</v>
+      </c>
+      <c r="B104" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="9">
+        <v>0</v>
+      </c>
+      <c r="B105" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="9">
+        <v>0</v>
+      </c>
+      <c r="B106" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="9">
+        <v>0</v>
+      </c>
+      <c r="B107" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="B108" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="B109" s="9">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="9">
+        <v>27.2</v>
+      </c>
+      <c r="B110" s="9">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="9">
+        <v>12.7</v>
+      </c>
+      <c r="B111" s="9">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="9">
+        <v>32.6</v>
+      </c>
+      <c r="B112" s="9">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="9">
+        <v>30.8</v>
+      </c>
+      <c r="B113" s="9">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="9">
+        <v>25.4</v>
+      </c>
+      <c r="B114" s="9">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="9">
+        <v>38.1</v>
+      </c>
+      <c r="B115" s="9">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="9">
+        <v>30.8</v>
+      </c>
+      <c r="B116" s="9">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="9">
+        <v>43.5</v>
+      </c>
+      <c r="B117" s="9">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="9">
+        <v>38.1</v>
+      </c>
+      <c r="B118" s="9">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="9">
+        <v>49</v>
+      </c>
+      <c r="B119" s="9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="9">
+        <v>38.1</v>
+      </c>
+      <c r="B120" s="9">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="9">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="B121" s="9">
+        <v>81.599999999999994</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="9">
+        <v>119.7</v>
+      </c>
+      <c r="B122" s="9">
+        <v>119.7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="9">
+        <v>88.9</v>
+      </c>
+      <c r="B123" s="9">
+        <v>88.9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="9">
+        <v>132.4</v>
+      </c>
+      <c r="B124" s="9">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="9">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="B125" s="9">
+        <v>154.19999999999999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="9">
+        <v>382.7</v>
+      </c>
+      <c r="B126" s="9">
+        <v>382.7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="9">
+        <v>94.3</v>
+      </c>
+      <c r="B127" s="9">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="9">
+        <v>63.5</v>
+      </c>
+      <c r="B128" s="9">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="9">
+        <v>79.8</v>
+      </c>
+      <c r="B129" s="9">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="9">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="B130" s="9">
+        <v>81.599999999999994</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="9">
+        <v>88.9</v>
+      </c>
+      <c r="B131" s="9">
+        <v>88.9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="9">
+        <v>65.3</v>
+      </c>
+      <c r="B132" s="9">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="9">
+        <v>63.5</v>
+      </c>
+      <c r="B133" s="9">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="9">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="B134" s="9">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="9">
+        <v>14.5</v>
+      </c>
+      <c r="B135" s="9">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="9">
+        <v>21.8</v>
+      </c>
+      <c r="B136" s="9">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="B137" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="B138" s="9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="9">
+        <v>0</v>
+      </c>
+      <c r="B139" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="9">
+        <v>0</v>
+      </c>
+      <c r="B140" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="9">
+        <v>0</v>
+      </c>
+      <c r="B141" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="9">
+        <v>0</v>
+      </c>
+      <c r="B142" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="9">
+        <v>0</v>
+      </c>
+      <c r="B143" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="9">
+        <v>0</v>
+      </c>
+      <c r="B144" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="9">
+        <v>0</v>
+      </c>
+      <c r="B145" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="9">
+        <v>0</v>
+      </c>
+      <c r="B146" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="9">
+        <v>0</v>
+      </c>
+      <c r="B147" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="9">
+        <v>0</v>
+      </c>
+      <c r="B148" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="9">
+        <v>0</v>
+      </c>
+      <c r="B149" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="9">
+        <v>0</v>
+      </c>
+      <c r="B150" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="9">
+        <v>0</v>
+      </c>
+      <c r="B151" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="9">
+        <v>0</v>
+      </c>
+      <c r="B152" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="B153" s="9">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="9">
+        <v>16.3</v>
+      </c>
+      <c r="B154" s="9">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="9">
+        <v>116.1</v>
+      </c>
+      <c r="B155" s="9">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="9">
+        <v>175.9</v>
+      </c>
+      <c r="B156" s="9">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="9">
+        <v>248.5</v>
+      </c>
+      <c r="B157" s="9">
+        <v>248.5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="9">
+        <v>295.60000000000002</v>
+      </c>
+      <c r="B158" s="9">
+        <v>295.60000000000002</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="9">
+        <v>366.4</v>
+      </c>
+      <c r="B159" s="9">
+        <v>366.4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="9">
+        <v>444.4</v>
+      </c>
+      <c r="B160" s="9">
+        <v>444.4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="9">
+        <v>527.79999999999995</v>
+      </c>
+      <c r="B161" s="9">
+        <v>527.79999999999995</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="9">
+        <v>594.9</v>
+      </c>
+      <c r="B162" s="9">
+        <v>594.9</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="9">
+        <v>663.8</v>
+      </c>
+      <c r="B163" s="9">
+        <v>663.8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="9">
+        <v>721.8</v>
+      </c>
+      <c r="B164" s="9">
+        <v>721.8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="9">
+        <v>787.1</v>
+      </c>
+      <c r="B165" s="9">
+        <v>787.1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="9">
+        <v>839.7</v>
+      </c>
+      <c r="B166" s="9">
+        <v>839.7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="9">
+        <v>877.8</v>
+      </c>
+      <c r="B167" s="9">
+        <v>877.8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="9">
+        <v>228.5</v>
+      </c>
+      <c r="B168" s="9">
+        <v>228.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="9">
+        <v>253.9</v>
+      </c>
+      <c r="B169" s="9">
+        <v>253.9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="9">
+        <v>277.5</v>
+      </c>
+      <c r="B170" s="9">
+        <v>277.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="9">
+        <v>179.6</v>
+      </c>
+      <c r="B171" s="9">
+        <v>179.6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="9">
+        <v>121.5</v>
+      </c>
+      <c r="B172" s="9">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="9">
+        <v>136</v>
+      </c>
+      <c r="B173" s="9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="9">
+        <v>181.4</v>
+      </c>
+      <c r="B174" s="9">
+        <v>181.4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="9">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="B175" s="9">
+        <v>152.30000000000001</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="9">
+        <v>348.2</v>
+      </c>
+      <c r="B176" s="9">
+        <v>348.2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="9">
+        <v>234</v>
+      </c>
+      <c r="B177" s="9">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="9">
+        <v>219.5</v>
+      </c>
+      <c r="B178" s="9">
+        <v>219.5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="9">
+        <v>161.4</v>
+      </c>
+      <c r="B179" s="9">
+        <v>161.4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="9">
+        <v>275.7</v>
+      </c>
+      <c r="B180" s="9">
+        <v>275.7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="9">
+        <v>127</v>
+      </c>
+      <c r="B181" s="9">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="9">
+        <v>45.3</v>
+      </c>
+      <c r="B182" s="9">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="9">
+        <v>30.8</v>
+      </c>
+      <c r="B183" s="9">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" s="9">
+        <v>25.4</v>
+      </c>
+      <c r="B184" s="9">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" s="9">
+        <v>12.7</v>
+      </c>
+      <c r="B185" s="9">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="B186" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" s="9">
+        <v>0</v>
+      </c>
+      <c r="B187" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" s="9">
+        <v>0</v>
+      </c>
+      <c r="B188" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" s="9">
+        <v>0</v>
+      </c>
+      <c r="B189" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" s="9">
+        <v>0</v>
+      </c>
+      <c r="B190" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" s="9">
+        <v>0</v>
+      </c>
+      <c r="B191" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" s="9">
+        <v>0</v>
+      </c>
+      <c r="B192" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" s="9">
+        <v>0</v>
+      </c>
+      <c r="B193" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" s="9">
+        <v>0</v>
+      </c>
+      <c r="B194" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" s="9">
+        <v>0</v>
+      </c>
+      <c r="B195" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" s="9">
+        <v>0</v>
+      </c>
+      <c r="B196" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" s="9">
+        <v>0</v>
+      </c>
+      <c r="B197" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" s="9">
+        <v>0</v>
+      </c>
+      <c r="B198" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" s="9">
+        <v>0</v>
+      </c>
+      <c r="B199" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" s="9">
+        <v>0</v>
+      </c>
+      <c r="B200" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="B201" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" s="9">
+        <v>20</v>
+      </c>
+      <c r="B202" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" s="9">
+        <v>70.7</v>
+      </c>
+      <c r="B203" s="9">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" s="9">
+        <v>58</v>
+      </c>
+      <c r="B204" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" s="9">
+        <v>117.9</v>
+      </c>
+      <c r="B205" s="9">
+        <v>117.9</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" s="9">
+        <v>248.5</v>
+      </c>
+      <c r="B206" s="9">
+        <v>248.5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" s="9">
+        <v>195.9</v>
+      </c>
+      <c r="B207" s="9">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" s="9">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="B208" s="9">
+        <v>154.19999999999999</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" s="9">
+        <v>145.1</v>
+      </c>
+      <c r="B209" s="9">
+        <v>145.1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" s="9">
+        <v>192.2</v>
+      </c>
+      <c r="B210" s="9">
+        <v>192.2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" s="9">
+        <v>166.9</v>
+      </c>
+      <c r="B211" s="9">
+        <v>166.9</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" s="9">
+        <v>208.6</v>
+      </c>
+      <c r="B212" s="9">
+        <v>208.6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" s="9">
+        <v>228.5</v>
+      </c>
+      <c r="B213" s="9">
+        <v>228.5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" s="9">
+        <v>234</v>
+      </c>
+      <c r="B214" s="9">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" s="9">
+        <v>279.3</v>
+      </c>
+      <c r="B215" s="9">
+        <v>279.3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" s="9">
+        <v>266.60000000000002</v>
+      </c>
+      <c r="B216" s="9">
+        <v>266.60000000000002</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" s="9">
+        <v>192.2</v>
+      </c>
+      <c r="B217" s="9">
+        <v>192.2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" s="9">
+        <v>185</v>
+      </c>
+      <c r="B218" s="9">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" s="9">
+        <v>284.7</v>
+      </c>
+      <c r="B219" s="9">
+        <v>284.7</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" s="9">
+        <v>186.8</v>
+      </c>
+      <c r="B220" s="9">
+        <v>186.8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" s="9">
+        <v>177.7</v>
+      </c>
+      <c r="B221" s="9">
+        <v>177.7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" s="9">
+        <v>192.2</v>
+      </c>
+      <c r="B222" s="9">
+        <v>192.2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" s="9">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="B223" s="9">
+        <v>137.80000000000001</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" s="9">
+        <v>219.5</v>
+      </c>
+      <c r="B224" s="9">
+        <v>219.5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="9">
+        <v>190.4</v>
+      </c>
+      <c r="B225" s="9">
+        <v>190.4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="9">
+        <v>248.5</v>
+      </c>
+      <c r="B226" s="9">
+        <v>248.5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="9">
+        <v>188.6</v>
+      </c>
+      <c r="B227" s="9">
+        <v>188.6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" s="9">
+        <v>210.4</v>
+      </c>
+      <c r="B228" s="9">
+        <v>210.4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="9">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="B229" s="9">
+        <v>137.80000000000001</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="9">
+        <v>78</v>
+      </c>
+      <c r="B230" s="9">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="9">
+        <v>107</v>
+      </c>
+      <c r="B231" s="9">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="9">
+        <v>39.9</v>
+      </c>
+      <c r="B232" s="9">
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="B233" s="9">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" s="9">
+        <v>1.8</v>
+      </c>
+      <c r="B234" s="9">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" s="9">
+        <v>0</v>
+      </c>
+      <c r="B235" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" s="9">
+        <v>0</v>
+      </c>
+      <c r="B236" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" s="9">
+        <v>0</v>
+      </c>
+      <c r="B237" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" s="9">
+        <v>0</v>
+      </c>
+      <c r="B238" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" s="9">
+        <v>0</v>
+      </c>
+      <c r="B239" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" s="9">
+        <v>0</v>
+      </c>
+      <c r="B240" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" s="9">
+        <v>0</v>
+      </c>
+      <c r="B241" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" s="9">
+        <v>0</v>
+      </c>
+      <c r="B242" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" s="9">
+        <v>0</v>
+      </c>
+      <c r="B243" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" s="9">
+        <v>0</v>
+      </c>
+      <c r="B244" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="9">
+        <v>0</v>
+      </c>
+      <c r="B245" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" s="9">
+        <v>0</v>
+      </c>
+      <c r="B246" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" s="9">
+        <v>0</v>
+      </c>
+      <c r="B247" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" s="9">
+        <v>0</v>
+      </c>
+      <c r="B248" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="B249" s="9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" s="9">
+        <v>10.9</v>
+      </c>
+      <c r="B250" s="9">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" s="9">
+        <v>16.3</v>
+      </c>
+      <c r="B251" s="9">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" s="9">
+        <v>25.4</v>
+      </c>
+      <c r="B252" s="9">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" s="9">
+        <v>342.8</v>
+      </c>
+      <c r="B253" s="9">
+        <v>342.8</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" s="9">
+        <v>214</v>
+      </c>
+      <c r="B254" s="9">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" s="9">
+        <v>59.9</v>
+      </c>
+      <c r="B255" s="9">
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" s="9">
+        <v>466.1</v>
+      </c>
+      <c r="B256" s="9">
+        <v>466.1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" s="9">
+        <v>515.1</v>
+      </c>
+      <c r="B257" s="9">
+        <v>515.1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" s="9">
+        <v>288.39999999999998</v>
+      </c>
+      <c r="B258" s="9">
+        <v>288.39999999999998</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" s="9">
+        <v>47.2</v>
+      </c>
+      <c r="B259" s="9">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" s="9">
+        <v>295.60000000000002</v>
+      </c>
+      <c r="B260" s="9">
+        <v>295.60000000000002</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" s="9">
+        <v>478.8</v>
+      </c>
+      <c r="B261" s="9">
+        <v>478.8</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" s="9">
+        <v>886.9</v>
+      </c>
+      <c r="B262" s="9">
+        <v>886.9</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" s="9">
+        <v>183.2</v>
+      </c>
+      <c r="B263" s="9">
+        <v>183.2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="9">
+        <v>97.9</v>
+      </c>
+      <c r="B264" s="9">
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="9">
+        <v>99.8</v>
+      </c>
+      <c r="B265" s="9">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="9">
+        <v>301.10000000000002</v>
+      </c>
+      <c r="B266" s="9">
+        <v>301.10000000000002</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="9">
+        <v>1024.7</v>
+      </c>
+      <c r="B267" s="9">
+        <v>1024.7</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="9">
+        <v>674.7</v>
+      </c>
+      <c r="B268" s="9">
+        <v>674.7</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="9">
+        <v>923.2</v>
+      </c>
+      <c r="B269" s="9">
+        <v>923.2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="9">
+        <v>65.3</v>
+      </c>
+      <c r="B270" s="9">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="9">
+        <v>76.2</v>
+      </c>
+      <c r="B271" s="9">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="9">
+        <v>72.5</v>
+      </c>
+      <c r="B272" s="9">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" s="9">
+        <v>49</v>
+      </c>
+      <c r="B273" s="9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" s="9">
+        <v>50.8</v>
+      </c>
+      <c r="B274" s="9">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" s="9">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="B275" s="9">
+        <v>81.599999999999994</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" s="9">
+        <v>108.8</v>
+      </c>
+      <c r="B276" s="9">
+        <v>108.8</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" s="9">
+        <v>63.5</v>
+      </c>
+      <c r="B277" s="9">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" s="9">
+        <v>47.2</v>
+      </c>
+      <c r="B278" s="9">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" s="9">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="B279" s="9">
+        <v>36.299999999999997</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" s="9">
+        <v>32.6</v>
+      </c>
+      <c r="B280" s="9">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" s="9">
+        <v>14.5</v>
+      </c>
+      <c r="B281" s="9">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="B282" s="9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" s="9">
+        <v>0</v>
+      </c>
+      <c r="B283" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" s="9">
+        <v>0</v>
+      </c>
+      <c r="B284" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" s="9">
+        <v>0</v>
+      </c>
+      <c r="B285" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" s="9">
+        <v>0</v>
+      </c>
+      <c r="B286" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" s="9">
+        <v>0</v>
+      </c>
+      <c r="B287" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" s="9">
+        <v>0</v>
+      </c>
+      <c r="B288" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" s="9">
+        <v>0</v>
+      </c>
+      <c r="B289" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" s="9">
+        <v>0</v>
+      </c>
+      <c r="B290" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" s="9">
+        <v>0</v>
+      </c>
+      <c r="B291" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" s="9">
+        <v>0</v>
+      </c>
+      <c r="B292" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" s="9">
+        <v>0</v>
+      </c>
+      <c r="B293" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" s="9">
+        <v>0</v>
+      </c>
+      <c r="B294" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" s="9">
+        <v>0</v>
+      </c>
+      <c r="B295" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" s="9">
+        <v>0</v>
+      </c>
+      <c r="B296" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" s="9">
+        <v>12.7</v>
+      </c>
+      <c r="B297" s="9">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" s="9">
+        <v>32.6</v>
+      </c>
+      <c r="B298" s="9">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" s="9">
+        <v>56.2</v>
+      </c>
+      <c r="B299" s="9">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" s="9">
+        <v>32.6</v>
+      </c>
+      <c r="B300" s="9">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301" s="9">
+        <v>97.9</v>
+      </c>
+      <c r="B301" s="9">
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302" s="9">
+        <v>141.5</v>
+      </c>
+      <c r="B302" s="9">
+        <v>141.5</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303" s="9">
+        <v>116.1</v>
+      </c>
+      <c r="B303" s="9">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304" s="9">
+        <v>210.4</v>
+      </c>
+      <c r="B304" s="9">
+        <v>210.4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305" s="9">
+        <v>174.1</v>
+      </c>
+      <c r="B305" s="9">
+        <v>174.1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306" s="9">
+        <v>92.5</v>
+      </c>
+      <c r="B306" s="9">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307" s="9">
+        <v>63.5</v>
+      </c>
+      <c r="B307" s="9">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308" s="9">
+        <v>45.3</v>
+      </c>
+      <c r="B308" s="9">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309" s="9">
+        <v>92.5</v>
+      </c>
+      <c r="B309" s="9">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310" s="9">
+        <v>58</v>
+      </c>
+      <c r="B310" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311" s="9">
+        <v>10.9</v>
+      </c>
+      <c r="B311" s="9">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312" s="9">
+        <v>134.19999999999999</v>
+      </c>
+      <c r="B312" s="9">
+        <v>134.19999999999999</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313" s="9">
+        <v>335.5</v>
+      </c>
+      <c r="B313" s="9">
+        <v>335.5</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314" s="9">
+        <v>117.9</v>
+      </c>
+      <c r="B314" s="9">
+        <v>117.9</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315" s="9">
+        <v>76.2</v>
+      </c>
+      <c r="B315" s="9">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316" s="9">
+        <v>79.8</v>
+      </c>
+      <c r="B316" s="9">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317" s="9">
+        <v>43.5</v>
+      </c>
+      <c r="B317" s="9">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318" s="9">
+        <v>43.5</v>
+      </c>
+      <c r="B318" s="9">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319" s="9">
+        <v>65.3</v>
+      </c>
+      <c r="B319" s="9">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320" s="9">
+        <v>49</v>
+      </c>
+      <c r="B320" s="9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321" s="9">
+        <v>23.6</v>
+      </c>
+      <c r="B321" s="9">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322" s="9">
+        <v>41.7</v>
+      </c>
+      <c r="B322" s="9">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323" s="9">
+        <v>27.2</v>
+      </c>
+      <c r="B323" s="9">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324" s="9">
+        <v>29</v>
+      </c>
+      <c r="B324" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325" s="9">
+        <v>16.3</v>
+      </c>
+      <c r="B325" s="9">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="B326" s="9">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="B327" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328" s="9">
+        <v>1.8</v>
+      </c>
+      <c r="B328" s="9">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329" s="9">
+        <v>0</v>
+      </c>
+      <c r="B329" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330" s="9">
+        <v>0</v>
+      </c>
+      <c r="B330" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A331" s="9">
+        <v>0</v>
+      </c>
+      <c r="B331" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332" s="9">
+        <v>0</v>
+      </c>
+      <c r="B332" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333" s="9">
+        <v>0</v>
+      </c>
+      <c r="B333" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334" s="9">
+        <v>0</v>
+      </c>
+      <c r="B334" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335" s="9">
+        <v>0</v>
+      </c>
+      <c r="B335" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336" s="9">
+        <v>0</v>
+      </c>
+      <c r="B336" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" s="9">
+        <v>0</v>
+      </c>
+      <c r="B337" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" s="9">
+        <v>0</v>
+      </c>
+      <c r="B338" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" s="9">
+        <v>0</v>
+      </c>
+      <c r="B339" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" s="9">
+        <v>0</v>
+      </c>
+      <c r="B340" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" s="9">
+        <v>0</v>
+      </c>
+      <c r="B341" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" s="9">
+        <v>0</v>
+      </c>
+      <c r="B342" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" s="9">
+        <v>0</v>
+      </c>
+      <c r="B343" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" s="9">
+        <v>0</v>
+      </c>
+      <c r="B344" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" s="9">
+        <v>0</v>
+      </c>
+      <c r="B345" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="B346" s="9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="B347" s="9">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" s="9">
+        <v>10.9</v>
+      </c>
+      <c r="B348" s="9">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" s="9">
+        <v>21.8</v>
+      </c>
+      <c r="B349" s="9">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" s="9">
+        <v>59.9</v>
+      </c>
+      <c r="B350" s="9">
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" s="9">
+        <v>92.5</v>
+      </c>
+      <c r="B351" s="9">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" s="9">
+        <v>132.4</v>
+      </c>
+      <c r="B352" s="9">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" s="9">
+        <v>141.5</v>
+      </c>
+      <c r="B353" s="9">
+        <v>141.5</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" s="9">
+        <v>208.6</v>
+      </c>
+      <c r="B354" s="9">
+        <v>208.6</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" s="9">
+        <v>297.39999999999998</v>
+      </c>
+      <c r="B355" s="9">
+        <v>297.39999999999998</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" s="9">
+        <v>112.4</v>
+      </c>
+      <c r="B356" s="9">
+        <v>112.4</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" s="9">
+        <v>163.19999999999999</v>
+      </c>
+      <c r="B357" s="9">
+        <v>163.19999999999999</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" s="9">
+        <v>237.6</v>
+      </c>
+      <c r="B358" s="9">
+        <v>237.6</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" s="9">
+        <v>235.8</v>
+      </c>
+      <c r="B359" s="9">
+        <v>235.8</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" s="9">
+        <v>244.8</v>
+      </c>
+      <c r="B360" s="9">
+        <v>244.8</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" s="9">
+        <v>214</v>
+      </c>
+      <c r="B361" s="9">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" s="9">
+        <v>277.5</v>
+      </c>
+      <c r="B362" s="9">
+        <v>277.5</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" s="9">
+        <v>183.2</v>
+      </c>
+      <c r="B363" s="9">
+        <v>183.2</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" s="9">
+        <v>273.89999999999998</v>
+      </c>
+      <c r="B364" s="9">
+        <v>273.89999999999998</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" s="9">
+        <v>264.8</v>
+      </c>
+      <c r="B365" s="9">
+        <v>264.8</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" s="9">
+        <v>277.5</v>
+      </c>
+      <c r="B366" s="9">
+        <v>277.5</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" s="9">
+        <v>331.9</v>
+      </c>
+      <c r="B367" s="9">
+        <v>331.9</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" s="9">
+        <v>175.9</v>
+      </c>
+      <c r="B368" s="9">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" s="9">
+        <v>224.9</v>
+      </c>
+      <c r="B369" s="9">
+        <v>224.9</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" s="9">
+        <v>150.5</v>
+      </c>
+      <c r="B370" s="9">
+        <v>150.5</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" s="9">
+        <v>130.6</v>
+      </c>
+      <c r="B371" s="9">
+        <v>130.6</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" s="9">
+        <v>119.7</v>
+      </c>
+      <c r="B372" s="9">
+        <v>119.7</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" s="9">
+        <v>78</v>
+      </c>
+      <c r="B373" s="9">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" s="9">
+        <v>74.400000000000006</v>
+      </c>
+      <c r="B374" s="9">
+        <v>74.400000000000006</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" s="9">
+        <v>38.1</v>
+      </c>
+      <c r="B375" s="9">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" s="9">
+        <v>39.9</v>
+      </c>
+      <c r="B376" s="9">
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" s="9">
+        <v>12.7</v>
+      </c>
+      <c r="B377" s="9">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" s="9">
+        <v>1.8</v>
+      </c>
+      <c r="B378" s="9">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" s="9">
+        <v>0</v>
+      </c>
+      <c r="B379" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" s="9">
+        <v>0</v>
+      </c>
+      <c r="B380" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" s="9">
+        <v>0</v>
+      </c>
+      <c r="B381" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382" s="9">
+        <v>0</v>
+      </c>
+      <c r="B382" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383" s="9">
+        <v>0</v>
+      </c>
+      <c r="B383" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384" s="9">
+        <v>0</v>
+      </c>
+      <c r="B384" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385" s="9">
+        <v>0</v>
+      </c>
+      <c r="B385" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386" s="9">
+        <v>0</v>
+      </c>
+      <c r="B386" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387" s="9">
+        <v>0</v>
+      </c>
+      <c r="B387" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388" s="9">
+        <v>0</v>
+      </c>
+      <c r="B388" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389" s="9">
+        <v>0</v>
+      </c>
+      <c r="B389" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390" s="9">
+        <v>0</v>
+      </c>
+      <c r="B390" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391" s="9">
+        <v>0</v>
+      </c>
+      <c r="B391" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392" s="9">
+        <v>0</v>
+      </c>
+      <c r="B392" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="B393" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394" s="9">
+        <v>14.5</v>
+      </c>
+      <c r="B394" s="9">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395" s="9">
+        <v>27.2</v>
+      </c>
+      <c r="B395" s="9">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396" s="9">
+        <v>195.9</v>
+      </c>
+      <c r="B396" s="9">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397" s="9">
+        <v>70.7</v>
+      </c>
+      <c r="B397" s="9">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398" s="9">
+        <v>301.10000000000002</v>
+      </c>
+      <c r="B398" s="9">
+        <v>301.10000000000002</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399" s="9">
+        <v>342.8</v>
+      </c>
+      <c r="B399" s="9">
+        <v>342.8</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400" s="9">
+        <v>438.9</v>
+      </c>
+      <c r="B400" s="9">
+        <v>438.9</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401" s="9">
+        <v>533.20000000000005</v>
+      </c>
+      <c r="B401" s="9">
+        <v>533.20000000000005</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402" s="9">
+        <v>600.29999999999995</v>
+      </c>
+      <c r="B402" s="9">
+        <v>600.29999999999995</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403" s="9">
+        <v>667.4</v>
+      </c>
+      <c r="B403" s="9">
+        <v>667.4</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A404" s="9">
+        <v>712.8</v>
+      </c>
+      <c r="B404" s="9">
+        <v>712.8</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A405" s="9">
+        <v>783.5</v>
+      </c>
+      <c r="B405" s="9">
+        <v>783.5</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A406" s="9">
+        <v>729.1</v>
+      </c>
+      <c r="B406" s="9">
+        <v>729.1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A407" s="9">
+        <v>866.9</v>
+      </c>
+      <c r="B407" s="9">
+        <v>866.9</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408" s="9">
+        <v>204.9</v>
+      </c>
+      <c r="B408" s="9">
+        <v>204.9</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A409" s="9">
+        <v>896</v>
+      </c>
+      <c r="B409" s="9">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A410" s="9">
+        <v>224.9</v>
+      </c>
+      <c r="B410" s="9">
+        <v>224.9</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A411" s="9">
+        <v>237.6</v>
+      </c>
+      <c r="B411" s="9">
+        <v>237.6</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A412" s="9">
+        <v>282.89999999999998</v>
+      </c>
+      <c r="B412" s="9">
+        <v>282.89999999999998</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413" s="9">
+        <v>277.5</v>
+      </c>
+      <c r="B413" s="9">
+        <v>277.5</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414" s="9">
+        <v>103.4</v>
+      </c>
+      <c r="B414" s="9">
+        <v>103.4</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A415" s="9">
+        <v>161.4</v>
+      </c>
+      <c r="B415" s="9">
+        <v>161.4</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A416" s="9">
+        <v>228.5</v>
+      </c>
+      <c r="B416" s="9">
+        <v>228.5</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A417" s="9">
+        <v>108.8</v>
+      </c>
+      <c r="B417" s="9">
+        <v>108.8</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A418" s="9">
+        <v>96.1</v>
+      </c>
+      <c r="B418" s="9">
+        <v>96.1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A419" s="9">
+        <v>94.3</v>
+      </c>
+      <c r="B419" s="9">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A420" s="9">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="B420" s="9">
+        <v>152.30000000000001</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A421" s="9">
+        <v>136</v>
+      </c>
+      <c r="B421" s="9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A422" s="9">
+        <v>30.8</v>
+      </c>
+      <c r="B422" s="9">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A423" s="9">
+        <v>21.8</v>
+      </c>
+      <c r="B423" s="9">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A424" s="9">
+        <v>39.9</v>
+      </c>
+      <c r="B424" s="9">
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A425" s="9">
+        <v>10.9</v>
+      </c>
+      <c r="B425" s="9">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A426" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="B426" s="9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A427" s="9">
+        <v>0</v>
+      </c>
+      <c r="B427" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A428" s="9">
+        <v>0</v>
+      </c>
+      <c r="B428" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A429" s="9">
+        <v>0</v>
+      </c>
+      <c r="B429" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A430" s="9">
+        <v>0</v>
+      </c>
+      <c r="B430" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A431" s="9">
+        <v>0</v>
+      </c>
+      <c r="B431" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A432" s="9">
+        <v>0</v>
+      </c>
+      <c r="B432" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A433" s="9">
+        <v>0</v>
+      </c>
+      <c r="B433" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A434" s="9">
+        <v>0</v>
+      </c>
+      <c r="B434" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A435" s="9">
+        <v>0</v>
+      </c>
+      <c r="B435" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A436" s="9">
+        <v>0</v>
+      </c>
+      <c r="B436" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A437" s="9">
+        <v>0</v>
+      </c>
+      <c r="B437" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A438" s="9">
+        <v>0</v>
+      </c>
+      <c r="B438" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A439" s="9">
+        <v>0</v>
+      </c>
+      <c r="B439" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A440" s="9">
+        <v>0</v>
+      </c>
+      <c r="B440" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A441" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="B441" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A442" s="9">
+        <v>14.5</v>
+      </c>
+      <c r="B442" s="9">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A443" s="9">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="B443" s="9">
+        <v>81.599999999999994</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A444" s="9">
+        <v>145.1</v>
+      </c>
+      <c r="B444" s="9">
+        <v>145.1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A445" s="9">
+        <v>223.1</v>
+      </c>
+      <c r="B445" s="9">
+        <v>223.1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A446" s="9">
+        <v>295.60000000000002</v>
+      </c>
+      <c r="B446" s="9">
+        <v>295.60000000000002</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A447" s="9">
+        <v>359.1</v>
+      </c>
+      <c r="B447" s="9">
+        <v>359.1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A448" s="9">
+        <v>440.7</v>
+      </c>
+      <c r="B448" s="9">
+        <v>440.7</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A449" s="9">
+        <v>516.9</v>
+      </c>
+      <c r="B449" s="9">
+        <v>516.9</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A450" s="9">
+        <v>582.20000000000005</v>
+      </c>
+      <c r="B450" s="9">
+        <v>582.20000000000005</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A451" s="9">
+        <v>651.1</v>
+      </c>
+      <c r="B451" s="9">
+        <v>651.1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A452" s="9">
+        <v>709.1</v>
+      </c>
+      <c r="B452" s="9">
+        <v>709.1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A453" s="9">
+        <v>828.8</v>
+      </c>
+      <c r="B453" s="9">
+        <v>828.8</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A454" s="9">
+        <v>243</v>
+      </c>
+      <c r="B454" s="9">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A455" s="9">
+        <v>127</v>
+      </c>
+      <c r="B455" s="9">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A456" s="9">
+        <v>331.9</v>
+      </c>
+      <c r="B456" s="9">
+        <v>331.9</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A457" s="9">
+        <v>208.6</v>
+      </c>
+      <c r="B457" s="9">
+        <v>208.6</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A458" s="9">
+        <v>114.3</v>
+      </c>
+      <c r="B458" s="9">
+        <v>114.3</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A459" s="9">
+        <v>47.2</v>
+      </c>
+      <c r="B459" s="9">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A460" s="9">
+        <v>234</v>
+      </c>
+      <c r="B460" s="9">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A461" s="9">
+        <v>59.9</v>
+      </c>
+      <c r="B461" s="9">
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A462" s="9">
+        <v>157.80000000000001</v>
+      </c>
+      <c r="B462" s="9">
+        <v>157.80000000000001</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A463" s="9">
+        <v>136</v>
+      </c>
+      <c r="B463" s="9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A464" s="9">
+        <v>194.1</v>
+      </c>
+      <c r="B464" s="9">
+        <v>194.1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A465" s="9">
+        <v>312</v>
+      </c>
+      <c r="B465" s="9">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A466" s="9">
+        <v>246.7</v>
+      </c>
+      <c r="B466" s="9">
+        <v>246.7</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A467" s="9">
+        <v>190.4</v>
+      </c>
+      <c r="B467" s="9">
+        <v>190.4</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A468" s="9">
+        <v>125.1</v>
+      </c>
+      <c r="B468" s="9">
+        <v>125.1</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A469" s="9">
+        <v>119.7</v>
+      </c>
+      <c r="B469" s="9">
+        <v>119.7</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A470" s="9">
+        <v>54.4</v>
+      </c>
+      <c r="B470" s="9">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A471" s="9">
+        <v>1.8</v>
+      </c>
+      <c r="B471" s="9">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A472" s="9">
+        <v>0</v>
+      </c>
+      <c r="B472" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A473" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="B473" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A474" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="B474" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A475" s="9">
+        <v>0</v>
+      </c>
+      <c r="B475" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A476" s="9">
+        <v>0</v>
+      </c>
+      <c r="B476" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A477" s="9">
+        <v>0</v>
+      </c>
+      <c r="B477" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A478" s="9">
+        <v>0</v>
+      </c>
+      <c r="B478" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A479" s="9">
+        <v>0</v>
+      </c>
+      <c r="B479" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A480" s="9">
+        <v>0</v>
+      </c>
+      <c r="B480" s="9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>